--- a/research/traditional_assets/database/data/romania/romania_trucking.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_trucking.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1059368505834899</v>
+        <v>0.1058051516225563</v>
       </c>
       <c r="C2">
-        <v>2.795875360839602</v>
+        <v>2.769498576796791</v>
       </c>
       <c r="D2">
-        <v>2.795875360839602</v>
+        <v>2.797298576796791</v>
       </c>
       <c r="E2">
-        <v>-0.36</v>
+        <v>-0.3322</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0278</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1439,28 +1439,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00139834</v>
       </c>
       <c r="N2">
-        <v>0.5289999999999999</v>
+        <v>0.5276016599999999</v>
       </c>
       <c r="O2">
-        <v>0.08463999999999999</v>
+        <v>0.08441626559999998</v>
       </c>
       <c r="P2">
-        <v>0.4443599999999999</v>
+        <v>0.4431853943999999</v>
       </c>
       <c r="Q2">
-        <v>0.8543599999999999</v>
+        <v>0.8531853943999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1059368505834899</v>
+        <v>0.1064471026490467</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919477</v>
+        <v>0.8348301958357582</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>378.3057053363273</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1058051516225563</v>
+        <v>0.1056734526616227</v>
       </c>
       <c r="C3">
-        <v>2.769498576796791</v>
+        <v>2.743123242443261</v>
       </c>
       <c r="D3">
-        <v>2.797298576796791</v>
+        <v>2.798723242443261</v>
       </c>
       <c r="E3">
-        <v>-0.3322</v>
+        <v>-0.3044</v>
       </c>
       <c r="F3">
-        <v>0.0278</v>
+        <v>0.0556</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1521,28 +1521,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M3">
-        <v>0.00139834</v>
+        <v>0.00279668</v>
       </c>
       <c r="N3">
-        <v>0.5276016599999999</v>
+        <v>0.5262033199999999</v>
       </c>
       <c r="O3">
-        <v>0.08441626559999998</v>
+        <v>0.08419253119999999</v>
       </c>
       <c r="P3">
-        <v>0.4431853943999999</v>
+        <v>0.4420107887999999</v>
       </c>
       <c r="Q3">
-        <v>0.8531853943999999</v>
+        <v>0.8520107887999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1064471026490467</v>
+        <v>0.106967768022064</v>
       </c>
       <c r="T3">
-        <v>0.8348301958357582</v>
+        <v>0.8419973506763812</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>378.3057053363273</v>
+        <v>189.1528526681637</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1056734526616227</v>
+        <v>0.1055417537006891</v>
       </c>
       <c r="C4">
-        <v>2.743123242443261</v>
+        <v>2.716749359995124</v>
       </c>
       <c r="D4">
-        <v>2.798723242443261</v>
+        <v>2.800149359995125</v>
       </c>
       <c r="E4">
-        <v>-0.3044</v>
+        <v>-0.2766</v>
       </c>
       <c r="F4">
-        <v>0.0556</v>
+        <v>0.08339999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1603,28 +1603,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M4">
-        <v>0.00279668</v>
+        <v>0.004195019999999999</v>
       </c>
       <c r="N4">
-        <v>0.5262033199999999</v>
+        <v>0.5248049799999999</v>
       </c>
       <c r="O4">
-        <v>0.08419253119999999</v>
+        <v>0.08396879679999998</v>
       </c>
       <c r="P4">
-        <v>0.4420107887999999</v>
+        <v>0.4408361831999999</v>
       </c>
       <c r="Q4">
-        <v>0.8520107887999999</v>
+        <v>0.8508361831999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.106967768022064</v>
+        <v>0.107499168763597</v>
       </c>
       <c r="T4">
-        <v>0.8419973506763812</v>
+        <v>0.8493122819054705</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>189.1528526681637</v>
+        <v>126.1019017787758</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1055417537006891</v>
+        <v>0.1054100547397555</v>
       </c>
       <c r="C5">
-        <v>2.716749359995124</v>
+        <v>2.69037693167301</v>
       </c>
       <c r="D5">
-        <v>2.800149359995125</v>
+        <v>2.80157693167301</v>
       </c>
       <c r="E5">
-        <v>-0.2766</v>
+        <v>-0.2488</v>
       </c>
       <c r="F5">
-        <v>0.08339999999999999</v>
+        <v>0.1112</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1685,28 +1685,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M5">
-        <v>0.004195019999999999</v>
+        <v>0.005593359999999999</v>
       </c>
       <c r="N5">
-        <v>0.5248049799999999</v>
+        <v>0.5234066399999999</v>
       </c>
       <c r="O5">
-        <v>0.08396879679999998</v>
+        <v>0.08374506239999999</v>
       </c>
       <c r="P5">
-        <v>0.4408361831999999</v>
+        <v>0.4396615775999999</v>
       </c>
       <c r="Q5">
-        <v>0.8508361831999999</v>
+        <v>0.8496615775999998</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.107499168763597</v>
+        <v>0.108041640353912</v>
       </c>
       <c r="T5">
-        <v>0.8493122819054705</v>
+        <v>0.8567796075351658</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>126.1019017787758</v>
+        <v>94.57642633408183</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1054100547397555</v>
+        <v>0.1052783557788219</v>
       </c>
       <c r="C6">
-        <v>2.69037693167301</v>
+        <v>2.664005959702081</v>
       </c>
       <c r="D6">
-        <v>2.80157693167301</v>
+        <v>2.803005959702081</v>
       </c>
       <c r="E6">
-        <v>-0.2488</v>
+        <v>-0.221</v>
       </c>
       <c r="F6">
-        <v>0.1112</v>
+        <v>0.139</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1767,28 +1767,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M6">
-        <v>0.005593359999999999</v>
+        <v>0.006991699999999999</v>
       </c>
       <c r="N6">
-        <v>0.5234066399999999</v>
+        <v>0.5220082999999999</v>
       </c>
       <c r="O6">
-        <v>0.08374506239999999</v>
+        <v>0.08352132799999998</v>
       </c>
       <c r="P6">
-        <v>0.4396615775999999</v>
+        <v>0.4384869719999999</v>
       </c>
       <c r="Q6">
-        <v>0.8496615775999998</v>
+        <v>0.8484869719999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.108041640353912</v>
+        <v>0.1085955323987599</v>
       </c>
       <c r="T6">
-        <v>0.8567796075351658</v>
+        <v>0.8644041400202234</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>94.57642633408183</v>
+        <v>75.66114106726546</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1052783557788219</v>
+        <v>0.1051466568178883</v>
       </c>
       <c r="C7">
-        <v>2.664005959702081</v>
+        <v>2.637636446312039</v>
       </c>
       <c r="D7">
-        <v>2.803005959702081</v>
+        <v>2.804436446312039</v>
       </c>
       <c r="E7">
-        <v>-0.221</v>
+        <v>-0.1932</v>
       </c>
       <c r="F7">
-        <v>0.139</v>
+        <v>0.1668</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1849,28 +1849,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M7">
-        <v>0.006991699999999999</v>
+        <v>0.00839004</v>
       </c>
       <c r="N7">
-        <v>0.5220082999999999</v>
+        <v>0.5206099599999999</v>
       </c>
       <c r="O7">
-        <v>0.08352132799999998</v>
+        <v>0.08329759359999998</v>
       </c>
       <c r="P7">
-        <v>0.4384869719999999</v>
+        <v>0.4373123663999999</v>
       </c>
       <c r="Q7">
-        <v>0.8484869719999999</v>
+        <v>0.8473123664</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1085955323987599</v>
+        <v>0.1091612093807323</v>
       </c>
       <c r="T7">
-        <v>0.8644041400202234</v>
+        <v>0.8721908966007076</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>75.66114106726546</v>
+        <v>63.05095088938788</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1051466568178883</v>
+        <v>0.1050149578569548</v>
       </c>
       <c r="C8">
-        <v>2.637636446312039</v>
+        <v>2.611268393737143</v>
       </c>
       <c r="D8">
-        <v>2.804436446312039</v>
+        <v>2.805868393737143</v>
       </c>
       <c r="E8">
-        <v>-0.1932</v>
+        <v>-0.1654</v>
       </c>
       <c r="F8">
-        <v>0.1668</v>
+        <v>0.1946</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1931,28 +1931,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M8">
-        <v>0.008390039999999998</v>
+        <v>0.009788379999999998</v>
       </c>
       <c r="N8">
-        <v>0.5206099599999999</v>
+        <v>0.5192116199999999</v>
       </c>
       <c r="O8">
-        <v>0.08329759359999998</v>
+        <v>0.08307385919999997</v>
       </c>
       <c r="P8">
-        <v>0.4373123663999999</v>
+        <v>0.4361377607999999</v>
       </c>
       <c r="Q8">
-        <v>0.8473123664</v>
+        <v>0.8461377607999998</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1091612093807323</v>
+        <v>0.1097390514590912</v>
       </c>
       <c r="T8">
-        <v>0.8721908966007076</v>
+        <v>0.8801451103119547</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>63.0509508893879</v>
+        <v>54.04367219090391</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1050149578569548</v>
+        <v>0.1048832588960212</v>
       </c>
       <c r="C9">
-        <v>2.611268393737143</v>
+        <v>2.584901804216215</v>
       </c>
       <c r="D9">
-        <v>2.805868393737143</v>
+        <v>2.807301804216215</v>
       </c>
       <c r="E9">
-        <v>-0.1654</v>
+        <v>-0.1376</v>
       </c>
       <c r="F9">
-        <v>0.1946</v>
+        <v>0.2224</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2013,28 +2013,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M9">
-        <v>0.009788379999999999</v>
+        <v>0.01118672</v>
       </c>
       <c r="N9">
-        <v>0.5192116199999999</v>
+        <v>0.5178132799999999</v>
       </c>
       <c r="O9">
-        <v>0.08307385919999997</v>
+        <v>0.08285012479999999</v>
       </c>
       <c r="P9">
-        <v>0.4361377607999999</v>
+        <v>0.4349631552</v>
       </c>
       <c r="Q9">
-        <v>0.8461377607999998</v>
+        <v>0.8449631551999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1097390514590912</v>
+        <v>0.1103294553217622</v>
       </c>
       <c r="T9">
-        <v>0.8801451103119547</v>
+        <v>0.8882722417125769</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>54.0436721909039</v>
+        <v>47.28821316704092</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1048832588960212</v>
+        <v>0.1047515599350876</v>
       </c>
       <c r="C10">
-        <v>2.584901804216215</v>
+        <v>2.558536679992657</v>
       </c>
       <c r="D10">
-        <v>2.807301804216215</v>
+        <v>2.808736679992657</v>
       </c>
       <c r="E10">
-        <v>-0.1376</v>
+        <v>-0.1098</v>
       </c>
       <c r="F10">
-        <v>0.2224</v>
+        <v>0.2502</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2095,28 +2095,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M10">
-        <v>0.01118672</v>
+        <v>0.01258506</v>
       </c>
       <c r="N10">
-        <v>0.5178132799999999</v>
+        <v>0.5164149399999999</v>
       </c>
       <c r="O10">
-        <v>0.08285012479999999</v>
+        <v>0.08262639039999999</v>
       </c>
       <c r="P10">
-        <v>0.4349631552</v>
+        <v>0.4337885495999999</v>
       </c>
       <c r="Q10">
-        <v>0.8449631551999999</v>
+        <v>0.8437885495999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1103294553217622</v>
+        <v>0.1109328350935029</v>
       </c>
       <c r="T10">
-        <v>0.8882722417125769</v>
+        <v>0.8965779913857402</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>47.28821316704092</v>
+        <v>42.03396725959193</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1047515599350876</v>
+        <v>0.104619860974154</v>
       </c>
       <c r="C11">
-        <v>2.558536679992657</v>
+        <v>2.532173023314458</v>
       </c>
       <c r="D11">
-        <v>2.808736679992657</v>
+        <v>2.810173023314458</v>
       </c>
       <c r="E11">
-        <v>-0.1098</v>
+        <v>-0.08200000000000002</v>
       </c>
       <c r="F11">
-        <v>0.2502</v>
+        <v>0.278</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2177,28 +2177,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M11">
-        <v>0.01258506</v>
+        <v>0.0139834</v>
       </c>
       <c r="N11">
-        <v>0.5164149399999999</v>
+        <v>0.5150165999999999</v>
       </c>
       <c r="O11">
-        <v>0.08262639039999999</v>
+        <v>0.08240265599999999</v>
       </c>
       <c r="P11">
-        <v>0.4337885495999999</v>
+        <v>0.432613944</v>
       </c>
       <c r="Q11">
-        <v>0.8437885495999999</v>
+        <v>0.842613944</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1109328350935029</v>
+        <v>0.1115496233046156</v>
       </c>
       <c r="T11">
-        <v>0.8965779913857402</v>
+        <v>0.9050683132738628</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>42.03396725959193</v>
+        <v>37.83057053363274</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.104619860974154</v>
+        <v>0.1044881620132204</v>
       </c>
       <c r="C12">
-        <v>2.532173023314458</v>
+        <v>2.505810836434207</v>
       </c>
       <c r="D12">
-        <v>2.810173023314458</v>
+        <v>2.811610836434207</v>
       </c>
       <c r="E12">
-        <v>-0.08200000000000002</v>
+        <v>-0.05420000000000003</v>
       </c>
       <c r="F12">
-        <v>0.278</v>
+        <v>0.3058</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2259,28 +2259,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M12">
-        <v>0.0139834</v>
+        <v>0.01538174</v>
       </c>
       <c r="N12">
-        <v>0.5150165999999999</v>
+        <v>0.5136182599999999</v>
       </c>
       <c r="O12">
-        <v>0.08240265599999999</v>
+        <v>0.08217892159999998</v>
       </c>
       <c r="P12">
-        <v>0.432613944</v>
+        <v>0.4314393383999999</v>
       </c>
       <c r="Q12">
-        <v>0.842613944</v>
+        <v>0.8414393383999998</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1115496233046156</v>
+        <v>0.1121802719249668</v>
       </c>
       <c r="T12">
-        <v>0.9050683132738628</v>
+        <v>0.9137494289122803</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>37.83057053363274</v>
+        <v>34.39142775784794</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1044881620132204</v>
+        <v>0.1043564630522869</v>
       </c>
       <c r="C13">
-        <v>2.505810836434207</v>
+        <v>2.479450121609107</v>
       </c>
       <c r="D13">
-        <v>2.811610836434207</v>
+        <v>2.813050121609107</v>
       </c>
       <c r="E13">
-        <v>-0.05420000000000003</v>
+        <v>-0.02640000000000003</v>
       </c>
       <c r="F13">
-        <v>0.3058</v>
+        <v>0.3336</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2341,28 +2341,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M13">
-        <v>0.01538174</v>
+        <v>0.01678008</v>
       </c>
       <c r="N13">
-        <v>0.5136182599999999</v>
+        <v>0.5122199199999999</v>
       </c>
       <c r="O13">
-        <v>0.08217892159999998</v>
+        <v>0.08195518719999999</v>
       </c>
       <c r="P13">
-        <v>0.4314393383999999</v>
+        <v>0.4302647327999999</v>
       </c>
       <c r="Q13">
-        <v>0.8414393383999998</v>
+        <v>0.8402647327999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1121802719249668</v>
+        <v>0.1128252534685078</v>
       </c>
       <c r="T13">
-        <v>0.9137494289122803</v>
+        <v>0.922627842633389</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>34.39142775784794</v>
+        <v>31.52547544469395</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1043564630522869</v>
+        <v>0.1042247640913533</v>
       </c>
       <c r="C14">
-        <v>2.479450121609107</v>
+        <v>2.453090881100985</v>
       </c>
       <c r="D14">
-        <v>2.813050121609107</v>
+        <v>2.814490881100985</v>
       </c>
       <c r="E14">
-        <v>-0.02640000000000003</v>
+        <v>0.001400000000000012</v>
       </c>
       <c r="F14">
-        <v>0.3336</v>
+        <v>0.3614</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2423,28 +2423,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M14">
-        <v>0.01678008</v>
+        <v>0.01817842</v>
       </c>
       <c r="N14">
-        <v>0.5122199199999999</v>
+        <v>0.5108215799999999</v>
       </c>
       <c r="O14">
-        <v>0.08195518719999999</v>
+        <v>0.08173145279999998</v>
       </c>
       <c r="P14">
-        <v>0.4302647327999999</v>
+        <v>0.4290901271999999</v>
       </c>
       <c r="Q14">
-        <v>0.8402647327999999</v>
+        <v>0.8390901271999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1128252534685078</v>
+        <v>0.1134850621739693</v>
       </c>
       <c r="T14">
-        <v>0.922627842633389</v>
+        <v>0.9317103578193509</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>31.52547544469395</v>
+        <v>29.10043887202517</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1042247640913533</v>
+        <v>0.1040930651304197</v>
       </c>
       <c r="C15">
-        <v>2.453090881100985</v>
+        <v>2.426733117176305</v>
       </c>
       <c r="D15">
-        <v>2.814490881100985</v>
+        <v>2.815933117176305</v>
       </c>
       <c r="E15">
-        <v>0.001400000000000012</v>
+        <v>0.0292</v>
       </c>
       <c r="F15">
-        <v>0.3614</v>
+        <v>0.3892</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2505,28 +2505,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M15">
-        <v>0.01817842</v>
+        <v>0.01957676</v>
       </c>
       <c r="N15">
-        <v>0.5108215799999999</v>
+        <v>0.5094232399999999</v>
       </c>
       <c r="O15">
-        <v>0.08173145279999998</v>
+        <v>0.0815077184</v>
       </c>
       <c r="P15">
-        <v>0.4290901271999999</v>
+        <v>0.4279155216</v>
       </c>
       <c r="Q15">
-        <v>0.8390901271999999</v>
+        <v>0.8379155215999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1134850621739693</v>
+        <v>0.1141602152679299</v>
       </c>
       <c r="T15">
-        <v>0.9317103578193509</v>
+        <v>0.9410040942887071</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>29.10043887202517</v>
+        <v>27.02183609545195</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1040930651304197</v>
+        <v>0.1039613661694861</v>
       </c>
       <c r="C16">
-        <v>2.426733117176305</v>
+        <v>2.400376832106176</v>
       </c>
       <c r="D16">
-        <v>2.815933117176305</v>
+        <v>2.817376832106176</v>
       </c>
       <c r="E16">
-        <v>0.0292</v>
+        <v>0.05700000000000005</v>
       </c>
       <c r="F16">
-        <v>0.3892</v>
+        <v>0.417</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2587,28 +2587,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M16">
-        <v>0.01957676</v>
+        <v>0.0209751</v>
       </c>
       <c r="N16">
-        <v>0.5094232399999999</v>
+        <v>0.5080248999999999</v>
       </c>
       <c r="O16">
-        <v>0.0815077184</v>
+        <v>0.08128398399999999</v>
       </c>
       <c r="P16">
-        <v>0.4279155216</v>
+        <v>0.4267409159999999</v>
       </c>
       <c r="Q16">
-        <v>0.8379155215999999</v>
+        <v>0.8367409159999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1141602152679299</v>
+        <v>0.1148512543170425</v>
       </c>
       <c r="T16">
-        <v>0.9410040942887071</v>
+        <v>0.9505165069102834</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>27.02183609545195</v>
+        <v>25.22038035575515</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1039613661694861</v>
+        <v>0.1038296672085525</v>
       </c>
       <c r="C17">
-        <v>2.400376832106176</v>
+        <v>2.374022028166371</v>
       </c>
       <c r="D17">
-        <v>2.817376832106176</v>
+        <v>2.818822028166371</v>
       </c>
       <c r="E17">
-        <v>0.057</v>
+        <v>0.08479999999999999</v>
       </c>
       <c r="F17">
-        <v>0.417</v>
+        <v>0.4448</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2669,28 +2669,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M17">
-        <v>0.0209751</v>
+        <v>0.02237344</v>
       </c>
       <c r="N17">
-        <v>0.5080248999999999</v>
+        <v>0.5066265599999999</v>
       </c>
       <c r="O17">
-        <v>0.08128398399999999</v>
+        <v>0.0810602496</v>
       </c>
       <c r="P17">
-        <v>0.4267409159999999</v>
+        <v>0.4255663103999999</v>
       </c>
       <c r="Q17">
-        <v>0.8367409159999999</v>
+        <v>0.8355663104</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1148512543170425</v>
+        <v>0.1155587466768482</v>
       </c>
       <c r="T17">
-        <v>0.9505165069102834</v>
+        <v>0.9602554055466593</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>25.22038035575516</v>
+        <v>23.64410658352046</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1038296672085525</v>
+        <v>0.1036979682476189</v>
       </c>
       <c r="C18">
-        <v>2.374022028166371</v>
+        <v>2.347668707637331</v>
       </c>
       <c r="D18">
-        <v>2.818822028166371</v>
+        <v>2.820268707637331</v>
       </c>
       <c r="E18">
-        <v>0.08479999999999999</v>
+        <v>0.1126</v>
       </c>
       <c r="F18">
-        <v>0.4448</v>
+        <v>0.4726</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2751,28 +2751,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M18">
-        <v>0.02237344</v>
+        <v>0.02377178</v>
       </c>
       <c r="N18">
-        <v>0.5066265599999999</v>
+        <v>0.5052282199999999</v>
       </c>
       <c r="O18">
-        <v>0.0810602496</v>
+        <v>0.08083651519999999</v>
       </c>
       <c r="P18">
-        <v>0.4255663103999999</v>
+        <v>0.4243917047999999</v>
       </c>
       <c r="Q18">
-        <v>0.8355663104</v>
+        <v>0.8343917047999998</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1155587466768482</v>
+        <v>0.116283287045324</v>
       </c>
       <c r="T18">
-        <v>0.9602554055466593</v>
+        <v>0.9702289764393335</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>23.64410658352046</v>
+        <v>22.25327678448984</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1036979682476189</v>
+        <v>0.1035662692866853</v>
       </c>
       <c r="C19">
-        <v>2.347668707637331</v>
+        <v>2.321316872804184</v>
       </c>
       <c r="D19">
-        <v>2.820268707637331</v>
+        <v>2.821716872804184</v>
       </c>
       <c r="E19">
-        <v>0.1126</v>
+        <v>0.1404000000000001</v>
       </c>
       <c r="F19">
-        <v>0.4726</v>
+        <v>0.5004000000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2833,28 +2833,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M19">
-        <v>0.02377178</v>
+        <v>0.02517012</v>
       </c>
       <c r="N19">
-        <v>0.5052282199999999</v>
+        <v>0.50382988</v>
       </c>
       <c r="O19">
-        <v>0.08083651519999999</v>
+        <v>0.08061278079999999</v>
       </c>
       <c r="P19">
-        <v>0.4243917047999999</v>
+        <v>0.4232170991999999</v>
       </c>
       <c r="Q19">
-        <v>0.8343917047999998</v>
+        <v>0.8332170991999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.116283287045324</v>
+        <v>0.1170254991301041</v>
       </c>
       <c r="T19">
-        <v>0.9702289764393335</v>
+        <v>0.9804458051586581</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>22.25327678448984</v>
+        <v>21.01698362979596</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1035662692866853</v>
+        <v>0.1034345703257517</v>
       </c>
       <c r="C20">
-        <v>2.321316872804184</v>
+        <v>2.294966525956752</v>
       </c>
       <c r="D20">
-        <v>2.821716872804184</v>
+        <v>2.823166525956752</v>
       </c>
       <c r="E20">
-        <v>0.1404</v>
+        <v>0.1682</v>
       </c>
       <c r="F20">
-        <v>0.5004</v>
+        <v>0.5282</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2915,28 +2915,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M20">
-        <v>0.02517012</v>
+        <v>0.02656846</v>
       </c>
       <c r="N20">
-        <v>0.50382988</v>
+        <v>0.5024315399999999</v>
       </c>
       <c r="O20">
-        <v>0.08061278079999999</v>
+        <v>0.08038904639999998</v>
       </c>
       <c r="P20">
-        <v>0.4232170991999999</v>
+        <v>0.4220424935999999</v>
       </c>
       <c r="Q20">
-        <v>0.8332170991999999</v>
+        <v>0.8320424935999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1170254991301041</v>
+        <v>0.1177860374391997</v>
       </c>
       <c r="T20">
-        <v>0.9804458051586581</v>
+        <v>0.9909149012537685</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.01698362979597</v>
+        <v>19.91082659664881</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1034345703257517</v>
+        <v>0.1033028713648182</v>
       </c>
       <c r="C21">
-        <v>2.294966525956752</v>
+        <v>2.268617669389566</v>
       </c>
       <c r="D21">
-        <v>2.823166525956752</v>
+        <v>2.824617669389566</v>
       </c>
       <c r="E21">
-        <v>0.1682</v>
+        <v>0.196</v>
       </c>
       <c r="F21">
-        <v>0.5282</v>
+        <v>0.5559999999999999</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2997,28 +2997,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M21">
-        <v>0.02656846</v>
+        <v>0.0279668</v>
       </c>
       <c r="N21">
-        <v>0.5024315399999999</v>
+        <v>0.5010332</v>
       </c>
       <c r="O21">
-        <v>0.08038904639999998</v>
+        <v>0.08016531199999999</v>
       </c>
       <c r="P21">
-        <v>0.4220424935999999</v>
+        <v>0.420867888</v>
       </c>
       <c r="Q21">
-        <v>0.8320424935999999</v>
+        <v>0.830867888</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1177860374391997</v>
+        <v>0.1185655892060227</v>
       </c>
       <c r="T21">
-        <v>0.9909149012537685</v>
+        <v>1.001645724751257</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>19.91082659664881</v>
+        <v>18.91528526681637</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1033028713648182</v>
+        <v>0.1031711724038846</v>
       </c>
       <c r="C22">
-        <v>2.268617669389566</v>
+        <v>2.242270305401876</v>
       </c>
       <c r="D22">
-        <v>2.824617669389566</v>
+        <v>2.826070305401876</v>
       </c>
       <c r="E22">
-        <v>0.196</v>
+        <v>0.2238</v>
       </c>
       <c r="F22">
-        <v>0.5559999999999999</v>
+        <v>0.5838</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3079,28 +3079,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M22">
-        <v>0.0279668</v>
+        <v>0.02936514</v>
       </c>
       <c r="N22">
-        <v>0.5010332</v>
+        <v>0.4996348599999999</v>
       </c>
       <c r="O22">
-        <v>0.08016531199999999</v>
+        <v>0.07994157759999998</v>
       </c>
       <c r="P22">
-        <v>0.420867888</v>
+        <v>0.4196932823999999</v>
       </c>
       <c r="Q22">
-        <v>0.830867888</v>
+        <v>0.8296932823999998</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1185655892060227</v>
+        <v>0.1193648764606134</v>
       </c>
       <c r="T22">
-        <v>1.001645724751257</v>
+        <v>1.012648214666403</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.91528526681637</v>
+        <v>18.01455739696797</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1031711724038846</v>
+        <v>0.103039473442951</v>
       </c>
       <c r="C23">
-        <v>2.242270305401877</v>
+        <v>2.215924436297667</v>
       </c>
       <c r="D23">
-        <v>2.826070305401877</v>
+        <v>2.827524436297667</v>
       </c>
       <c r="E23">
-        <v>0.2238</v>
+        <v>0.2515999999999999</v>
       </c>
       <c r="F23">
-        <v>0.5838</v>
+        <v>0.6115999999999999</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3161,28 +3161,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M23">
-        <v>0.02936514</v>
+        <v>0.03076348</v>
       </c>
       <c r="N23">
-        <v>0.4996348599999999</v>
+        <v>0.4982365199999999</v>
       </c>
       <c r="O23">
-        <v>0.07994157759999998</v>
+        <v>0.07971784319999999</v>
       </c>
       <c r="P23">
-        <v>0.4196932823999999</v>
+        <v>0.4185186767999999</v>
       </c>
       <c r="Q23">
-        <v>0.8296932823999998</v>
+        <v>0.8285186767999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1193648764606134</v>
+        <v>0.1201846582601936</v>
       </c>
       <c r="T23">
-        <v>1.012648214666403</v>
+        <v>1.023932819707578</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.01455739696797</v>
+        <v>17.19571387892397</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.103039473442951</v>
+        <v>0.1029077744820174</v>
       </c>
       <c r="C24">
-        <v>2.215924436297667</v>
+        <v>2.189580064385664</v>
       </c>
       <c r="D24">
-        <v>2.827524436297667</v>
+        <v>2.828980064385664</v>
       </c>
       <c r="E24">
-        <v>0.2515999999999999</v>
+        <v>0.2794</v>
       </c>
       <c r="F24">
-        <v>0.6115999999999999</v>
+        <v>0.6394</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3243,28 +3243,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M24">
-        <v>0.03076348</v>
+        <v>0.03216181999999999</v>
       </c>
       <c r="N24">
-        <v>0.4982365199999999</v>
+        <v>0.4968381799999999</v>
       </c>
       <c r="O24">
-        <v>0.07971784319999999</v>
+        <v>0.07949410879999999</v>
       </c>
       <c r="P24">
-        <v>0.4185186767999999</v>
+        <v>0.4173440711999999</v>
       </c>
       <c r="Q24">
-        <v>0.8285186767999999</v>
+        <v>0.8273440712</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1201846582601936</v>
+        <v>0.1210257330935291</v>
       </c>
       <c r="T24">
-        <v>1.023932819707578</v>
+        <v>1.0355105313732</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.19571387892397</v>
+        <v>16.44807414505771</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1029077744820174</v>
+        <v>0.1027760755210838</v>
       </c>
       <c r="C25">
-        <v>2.189580064385664</v>
+        <v>2.163237191979353</v>
       </c>
       <c r="D25">
-        <v>2.828980064385664</v>
+        <v>2.830437191979353</v>
       </c>
       <c r="E25">
-        <v>0.2794</v>
+        <v>0.3072</v>
       </c>
       <c r="F25">
-        <v>0.6394</v>
+        <v>0.6672</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3325,28 +3325,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M25">
-        <v>0.03216181999999999</v>
+        <v>0.03356016</v>
       </c>
       <c r="N25">
-        <v>0.4968381799999999</v>
+        <v>0.4954398399999999</v>
       </c>
       <c r="O25">
-        <v>0.07949410879999999</v>
+        <v>0.07927037439999998</v>
       </c>
       <c r="P25">
-        <v>0.4173440711999999</v>
+        <v>0.4161694655999999</v>
       </c>
       <c r="Q25">
-        <v>0.8273440712</v>
+        <v>0.8261694655999998</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1210257330935291</v>
+        <v>0.1218889414751103</v>
       </c>
       <c r="T25">
-        <v>1.0355105313732</v>
+        <v>1.047392919661601</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.44807414505771</v>
+        <v>15.76273772234697</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1027760755210838</v>
+        <v>0.1026443765601503</v>
       </c>
       <c r="C26">
-        <v>2.163237191979353</v>
+        <v>2.136895821396985</v>
       </c>
       <c r="D26">
-        <v>2.830437191979353</v>
+        <v>2.831895821396984</v>
       </c>
       <c r="E26">
-        <v>0.3071999999999999</v>
+        <v>0.335</v>
       </c>
       <c r="F26">
-        <v>0.6671999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3407,28 +3407,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M26">
-        <v>0.03356015999999999</v>
+        <v>0.0349585</v>
       </c>
       <c r="N26">
-        <v>0.4954398399999999</v>
+        <v>0.4940414999999999</v>
       </c>
       <c r="O26">
-        <v>0.07927037439999998</v>
+        <v>0.07904663999999999</v>
       </c>
       <c r="P26">
-        <v>0.4161694655999999</v>
+        <v>0.4149948599999999</v>
       </c>
       <c r="Q26">
-        <v>0.8261694655999998</v>
+        <v>0.8249948599999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1218889414751103</v>
+        <v>0.122775168746867</v>
       </c>
       <c r="T26">
-        <v>1.047392919661601</v>
+        <v>1.059592171637693</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.76273772234697</v>
+        <v>15.13222821345309</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1026443765601503</v>
+        <v>0.1025126775992167</v>
       </c>
       <c r="C27">
-        <v>2.136895821396985</v>
+        <v>2.110555954961595</v>
       </c>
       <c r="D27">
-        <v>2.831895821396984</v>
+        <v>2.833355954961595</v>
       </c>
       <c r="E27">
-        <v>0.335</v>
+        <v>0.3628</v>
       </c>
       <c r="F27">
-        <v>0.695</v>
+        <v>0.7228</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3489,28 +3489,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M27">
-        <v>0.0349585</v>
+        <v>0.03635684</v>
       </c>
       <c r="N27">
-        <v>0.4940414999999999</v>
+        <v>0.4926431599999999</v>
       </c>
       <c r="O27">
-        <v>0.07904663999999999</v>
+        <v>0.07882290559999999</v>
       </c>
       <c r="P27">
-        <v>0.4149948599999999</v>
+        <v>0.4138202543999999</v>
       </c>
       <c r="Q27">
-        <v>0.8249948599999999</v>
+        <v>0.8238202544</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.122775168746867</v>
+        <v>0.1236853481070496</v>
       </c>
       <c r="T27">
-        <v>1.059592171637693</v>
+        <v>1.072121133126652</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.13222821345309</v>
+        <v>14.55021943601259</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1025126775992167</v>
+        <v>0.1023809786382831</v>
       </c>
       <c r="C28">
-        <v>2.110555954961595</v>
+        <v>2.084217595001011</v>
       </c>
       <c r="D28">
-        <v>2.833355954961595</v>
+        <v>2.834817595001011</v>
       </c>
       <c r="E28">
-        <v>0.3628</v>
+        <v>0.3906000000000001</v>
       </c>
       <c r="F28">
-        <v>0.7228</v>
+        <v>0.7506</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3571,28 +3571,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M28">
-        <v>0.03635684</v>
+        <v>0.03775518</v>
       </c>
       <c r="N28">
-        <v>0.4926431599999999</v>
+        <v>0.4912448199999999</v>
       </c>
       <c r="O28">
-        <v>0.07882290559999999</v>
+        <v>0.07859917119999998</v>
       </c>
       <c r="P28">
-        <v>0.4138202543999999</v>
+        <v>0.4126456487999999</v>
       </c>
       <c r="Q28">
-        <v>0.8238202544</v>
+        <v>0.8226456487999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1236853481070496</v>
+        <v>0.124620463888059</v>
       </c>
       <c r="T28">
-        <v>1.072121133126652</v>
+        <v>1.084993353834487</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.55021943601259</v>
+        <v>14.01132241986397</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1023809786382831</v>
+        <v>0.1022492796773495</v>
       </c>
       <c r="C29">
-        <v>2.084217595001011</v>
+        <v>2.057880743847865</v>
       </c>
       <c r="D29">
-        <v>2.834817595001011</v>
+        <v>2.836280743847865</v>
       </c>
       <c r="E29">
-        <v>0.3906000000000001</v>
+        <v>0.4184</v>
       </c>
       <c r="F29">
-        <v>0.7506</v>
+        <v>0.7784</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3653,28 +3653,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M29">
-        <v>0.03775518</v>
+        <v>0.03915352</v>
       </c>
       <c r="N29">
-        <v>0.4912448199999999</v>
+        <v>0.4898464799999999</v>
       </c>
       <c r="O29">
-        <v>0.07859917119999998</v>
+        <v>0.07837543679999999</v>
       </c>
       <c r="P29">
-        <v>0.4126456487999999</v>
+        <v>0.4114710431999999</v>
       </c>
       <c r="Q29">
-        <v>0.8226456487999999</v>
+        <v>0.8214710431999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.124620463888059</v>
+        <v>0.1255815551074299</v>
       </c>
       <c r="T29">
-        <v>1.084993353834487</v>
+        <v>1.098223136228651</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.01132241986397</v>
+        <v>13.51091804772598</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1022492796773495</v>
+        <v>0.1021175807164159</v>
       </c>
       <c r="C30">
-        <v>2.057880743847865</v>
+        <v>2.031545403839612</v>
       </c>
       <c r="D30">
-        <v>2.836280743847865</v>
+        <v>2.837745403839612</v>
       </c>
       <c r="E30">
-        <v>0.4184</v>
+        <v>0.4462</v>
       </c>
       <c r="F30">
-        <v>0.7784</v>
+        <v>0.8062</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3735,28 +3735,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M30">
-        <v>0.03915352</v>
+        <v>0.04055186</v>
       </c>
       <c r="N30">
-        <v>0.4898464799999999</v>
+        <v>0.4884481399999999</v>
       </c>
       <c r="O30">
-        <v>0.07837543679999999</v>
+        <v>0.07815170239999999</v>
       </c>
       <c r="P30">
-        <v>0.4114710431999999</v>
+        <v>0.4102964375999999</v>
       </c>
       <c r="Q30">
-        <v>0.8214710431999999</v>
+        <v>0.8202964375999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1255815551074299</v>
+        <v>0.1265697193188957</v>
       </c>
       <c r="T30">
-        <v>1.098223136228651</v>
+        <v>1.11182558854941</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.51091804772598</v>
+        <v>13.04502432194232</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1021175807164159</v>
+        <v>0.1023638817554823</v>
       </c>
       <c r="C31">
-        <v>2.031545403839612</v>
+        <v>2.001007452643536</v>
       </c>
       <c r="D31">
-        <v>2.837745403839612</v>
+        <v>2.835007452643536</v>
       </c>
       <c r="E31">
-        <v>0.4461999999999999</v>
+        <v>0.474</v>
       </c>
       <c r="F31">
-        <v>0.8061999999999999</v>
+        <v>0.834</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3817,45 +3817,45 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M31">
-        <v>0.04055186</v>
+        <v>0.0432012</v>
       </c>
       <c r="N31">
-        <v>0.4884481399999999</v>
+        <v>0.4857987999999999</v>
       </c>
       <c r="O31">
-        <v>0.07815170239999999</v>
+        <v>0.077727808</v>
       </c>
       <c r="P31">
-        <v>0.4102964375999999</v>
+        <v>0.4080709919999999</v>
       </c>
       <c r="Q31">
-        <v>0.8202964375999999</v>
+        <v>0.8180709919999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1265697193188957</v>
+        <v>0.1275861167935462</v>
       </c>
       <c r="T31">
-        <v>1.11182558854941</v>
+        <v>1.125816682365049</v>
       </c>
       <c r="U31">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V31">
         <v>0.16</v>
       </c>
       <c r="W31">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y31">
-        <v>13.04502432194232</v>
+        <v>12.24503023064174</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1023638817554823</v>
+        <v>0.1022447827945488</v>
       </c>
       <c r="C32">
-        <v>2.001007452643536</v>
+        <v>1.974530729973971</v>
       </c>
       <c r="D32">
-        <v>2.835007452643536</v>
+        <v>2.836330729973971</v>
       </c>
       <c r="E32">
-        <v>0.474</v>
+        <v>0.5017999999999999</v>
       </c>
       <c r="F32">
-        <v>0.834</v>
+        <v>0.8617999999999999</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3899,28 +3899,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M32">
-        <v>0.0432012</v>
+        <v>0.04464123999999999</v>
       </c>
       <c r="N32">
-        <v>0.4857987999999999</v>
+        <v>0.4843587599999999</v>
       </c>
       <c r="O32">
-        <v>0.077727808</v>
+        <v>0.07749740159999999</v>
       </c>
       <c r="P32">
-        <v>0.4080709919999999</v>
+        <v>0.4068613583999999</v>
       </c>
       <c r="Q32">
-        <v>0.8180709919999999</v>
+        <v>0.8168613584</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1275861167935462</v>
+        <v>0.1286319750645634</v>
       </c>
       <c r="T32">
-        <v>1.125816682365049</v>
+        <v>1.140213315131865</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>12.24503023064174</v>
+        <v>11.85002925545975</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1022447827945488</v>
+        <v>0.1021256838336152</v>
       </c>
       <c r="C33">
-        <v>1.974530729973971</v>
+        <v>1.948055243195767</v>
       </c>
       <c r="D33">
-        <v>2.836330729973971</v>
+        <v>2.837655243195766</v>
       </c>
       <c r="E33">
-        <v>0.5017999999999999</v>
+        <v>0.5296</v>
       </c>
       <c r="F33">
-        <v>0.8617999999999999</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3981,28 +3981,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M33">
-        <v>0.04464123999999999</v>
+        <v>0.04608128</v>
       </c>
       <c r="N33">
-        <v>0.4843587599999999</v>
+        <v>0.4829187199999999</v>
       </c>
       <c r="O33">
-        <v>0.07749740159999999</v>
+        <v>0.07726699519999999</v>
       </c>
       <c r="P33">
-        <v>0.4068613583999999</v>
+        <v>0.4056517247999999</v>
       </c>
       <c r="Q33">
-        <v>0.8168613584</v>
+        <v>0.8156517247999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1286319750645634</v>
+        <v>0.1297085938729635</v>
       </c>
       <c r="T33">
-        <v>1.140213315131865</v>
+        <v>1.155033378274176</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.85002925545975</v>
+        <v>11.47971584122663</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1021256838336152</v>
+        <v>0.1020065848726816</v>
       </c>
       <c r="C34">
-        <v>1.948055243195767</v>
+        <v>1.921580994041143</v>
       </c>
       <c r="D34">
-        <v>2.837655243195766</v>
+        <v>2.838980994041143</v>
       </c>
       <c r="E34">
-        <v>0.5296</v>
+        <v>0.5574</v>
       </c>
       <c r="F34">
-        <v>0.8895999999999999</v>
+        <v>0.9174</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4063,28 +4063,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M34">
-        <v>0.04608128</v>
+        <v>0.04752132</v>
       </c>
       <c r="N34">
-        <v>0.4829187199999999</v>
+        <v>0.4814786799999999</v>
       </c>
       <c r="O34">
-        <v>0.07726699519999999</v>
+        <v>0.07703658879999999</v>
       </c>
       <c r="P34">
-        <v>0.4056517247999999</v>
+        <v>0.4044420912</v>
       </c>
       <c r="Q34">
-        <v>0.8156517247999999</v>
+        <v>0.8144420911999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1297085938729635</v>
+        <v>0.1308173505562412</v>
       </c>
       <c r="T34">
-        <v>1.155033378274176</v>
+        <v>1.170295831361034</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.47971584122663</v>
+        <v>11.13184566421976</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1020065848726816</v>
+        <v>0.101887485911748</v>
       </c>
       <c r="C35">
-        <v>1.921580994041143</v>
+        <v>1.895107984245563</v>
       </c>
       <c r="D35">
-        <v>2.838980994041143</v>
+        <v>2.840307984245563</v>
       </c>
       <c r="E35">
-        <v>0.5574</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="F35">
-        <v>0.9174</v>
+        <v>0.9452</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4145,28 +4145,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M35">
-        <v>0.04752132</v>
+        <v>0.04896136</v>
       </c>
       <c r="N35">
-        <v>0.4814786799999999</v>
+        <v>0.4800386399999999</v>
       </c>
       <c r="O35">
-        <v>0.07703658879999999</v>
+        <v>0.07680618239999999</v>
       </c>
       <c r="P35">
-        <v>0.4044420912</v>
+        <v>0.4032324575999999</v>
       </c>
       <c r="Q35">
-        <v>0.8144420911999999</v>
+        <v>0.8132324575999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1308173505562412</v>
+        <v>0.1319597059268909</v>
       </c>
       <c r="T35">
-        <v>1.170295831361034</v>
+        <v>1.186020783026282</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.13184566421976</v>
+        <v>10.80443843880153</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.101887485911748</v>
+        <v>0.1017683869508144</v>
       </c>
       <c r="C36">
-        <v>1.895107984245563</v>
+        <v>1.868636215547736</v>
       </c>
       <c r="D36">
-        <v>2.840307984245563</v>
+        <v>2.841636215547736</v>
       </c>
       <c r="E36">
-        <v>0.5852000000000001</v>
+        <v>0.613</v>
       </c>
       <c r="F36">
-        <v>0.9452</v>
+        <v>0.973</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4227,28 +4227,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M36">
-        <v>0.04896136</v>
+        <v>0.0504014</v>
       </c>
       <c r="N36">
-        <v>0.4800386399999999</v>
+        <v>0.4785985999999999</v>
       </c>
       <c r="O36">
-        <v>0.07680618239999999</v>
+        <v>0.07657577599999998</v>
       </c>
       <c r="P36">
-        <v>0.4032324575999999</v>
+        <v>0.4020228239999999</v>
       </c>
       <c r="Q36">
-        <v>0.8132324575999998</v>
+        <v>0.8120228239999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1319597059268909</v>
+        <v>0.1331372106935606</v>
       </c>
       <c r="T36">
-        <v>1.186020783026282</v>
+        <v>1.202229579358152</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.80443843880153</v>
+        <v>10.49574019769292</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1017683869508144</v>
+        <v>0.1016492879898808</v>
       </c>
       <c r="C37">
-        <v>1.868636215547736</v>
+        <v>1.842165689689622</v>
       </c>
       <c r="D37">
-        <v>2.841636215547736</v>
+        <v>2.842965689689622</v>
       </c>
       <c r="E37">
-        <v>0.613</v>
+        <v>0.6408000000000001</v>
       </c>
       <c r="F37">
-        <v>0.973</v>
+        <v>1.0008</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4309,28 +4309,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M37">
-        <v>0.0504014</v>
+        <v>0.05184144</v>
       </c>
       <c r="N37">
-        <v>0.4785985999999999</v>
+        <v>0.4771585599999999</v>
       </c>
       <c r="O37">
-        <v>0.07657577599999998</v>
+        <v>0.07634536959999999</v>
       </c>
       <c r="P37">
-        <v>0.4020228239999999</v>
+        <v>0.4008131903999999</v>
       </c>
       <c r="Q37">
-        <v>0.8120228239999999</v>
+        <v>0.8108131903999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1331372106935606</v>
+        <v>0.1343515124841888</v>
       </c>
       <c r="T37">
-        <v>1.202229579358152</v>
+        <v>1.218944900575393</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.49574019769292</v>
+        <v>10.20419185886812</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1016492879898808</v>
+        <v>0.1015301890289473</v>
       </c>
       <c r="C38">
-        <v>1.842165689689622</v>
+        <v>1.815696408416446</v>
       </c>
       <c r="D38">
-        <v>2.842965689689622</v>
+        <v>2.844296408416446</v>
       </c>
       <c r="E38">
-        <v>0.6407999999999999</v>
+        <v>0.6686</v>
       </c>
       <c r="F38">
-        <v>1.0008</v>
+        <v>1.0286</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4391,28 +4391,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M38">
-        <v>0.05184144</v>
+        <v>0.05328148</v>
       </c>
       <c r="N38">
-        <v>0.4771585599999999</v>
+        <v>0.4757185199999999</v>
       </c>
       <c r="O38">
-        <v>0.07634536959999999</v>
+        <v>0.07611496319999998</v>
       </c>
       <c r="P38">
-        <v>0.4008131903999999</v>
+        <v>0.3996035567999999</v>
       </c>
       <c r="Q38">
-        <v>0.8108131903999999</v>
+        <v>0.8096035568</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1343515124841888</v>
+        <v>0.1356043635380115</v>
       </c>
       <c r="T38">
-        <v>1.218944900575393</v>
+        <v>1.236190866910642</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.20419185886812</v>
+        <v>9.928402889709519</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1015301890289473</v>
+        <v>0.1019537300680137</v>
       </c>
       <c r="C39">
-        <v>1.815696408416446</v>
+        <v>1.783169744586134</v>
       </c>
       <c r="D39">
-        <v>2.844296408416446</v>
+        <v>2.839569744586134</v>
       </c>
       <c r="E39">
-        <v>0.6686</v>
+        <v>0.6964</v>
       </c>
       <c r="F39">
-        <v>1.0286</v>
+        <v>1.0564</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4473,45 +4473,45 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M39">
-        <v>0.05328148</v>
+        <v>0.0565174</v>
       </c>
       <c r="N39">
-        <v>0.4757185199999999</v>
+        <v>0.4724825999999999</v>
       </c>
       <c r="O39">
-        <v>0.07611496319999998</v>
+        <v>0.07559721599999999</v>
       </c>
       <c r="P39">
-        <v>0.3996035567999999</v>
+        <v>0.396885384</v>
       </c>
       <c r="Q39">
-        <v>0.8096035568</v>
+        <v>0.8068853839999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1356043635380115</v>
+        <v>0.1368976291419575</v>
       </c>
       <c r="T39">
-        <v>1.236190866910642</v>
+        <v>1.253993154740576</v>
       </c>
       <c r="U39">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V39">
         <v>0.16</v>
       </c>
       <c r="W39">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>9.928402889709519</v>
+        <v>9.359949325340512</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1019537300680137</v>
+        <v>0.1018489111070801</v>
       </c>
       <c r="C40">
-        <v>1.783169744586134</v>
+        <v>1.756538047347434</v>
       </c>
       <c r="D40">
-        <v>2.839569744586134</v>
+        <v>2.840738047347434</v>
       </c>
       <c r="E40">
-        <v>0.6964</v>
+        <v>0.7242000000000001</v>
       </c>
       <c r="F40">
-        <v>1.0564</v>
+        <v>1.0842</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4555,28 +4555,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M40">
-        <v>0.0565174</v>
+        <v>0.0580047</v>
       </c>
       <c r="N40">
-        <v>0.4724825999999999</v>
+        <v>0.4709952999999999</v>
       </c>
       <c r="O40">
-        <v>0.07559721599999999</v>
+        <v>0.07535924799999999</v>
       </c>
       <c r="P40">
-        <v>0.396885384</v>
+        <v>0.3956360519999999</v>
       </c>
       <c r="Q40">
-        <v>0.8068853839999999</v>
+        <v>0.8056360519999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1368976291419575</v>
+        <v>0.1382332968968526</v>
       </c>
       <c r="T40">
-        <v>1.253993154740576</v>
+        <v>1.272379124138705</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>9.359949325340512</v>
+        <v>9.119950624690755</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1018489111070801</v>
+        <v>0.1017440921461465</v>
       </c>
       <c r="C41">
-        <v>1.756538047347434</v>
+        <v>1.729907311869338</v>
       </c>
       <c r="D41">
-        <v>2.840738047347434</v>
+        <v>2.841907311869338</v>
       </c>
       <c r="E41">
-        <v>0.7242000000000001</v>
+        <v>0.7519999999999999</v>
       </c>
       <c r="F41">
-        <v>1.0842</v>
+        <v>1.112</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4637,28 +4637,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M41">
-        <v>0.0580047</v>
+        <v>0.05949199999999999</v>
       </c>
       <c r="N41">
-        <v>0.4709952999999999</v>
+        <v>0.4695079999999999</v>
       </c>
       <c r="O41">
-        <v>0.07535924799999999</v>
+        <v>0.07512127999999998</v>
       </c>
       <c r="P41">
-        <v>0.3956360519999999</v>
+        <v>0.39438672</v>
       </c>
       <c r="Q41">
-        <v>0.8056360519999999</v>
+        <v>0.8043867199999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1382332968968526</v>
+        <v>0.1396134869102442</v>
       </c>
       <c r="T41">
-        <v>1.272379124138705</v>
+        <v>1.291377959183438</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.119950624690755</v>
+        <v>8.89195185907349</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1017440921461465</v>
+        <v>0.1016392731852129</v>
       </c>
       <c r="C42">
-        <v>1.729907311869338</v>
+        <v>1.703277539339934</v>
       </c>
       <c r="D42">
-        <v>2.841907311869338</v>
+        <v>2.843077539339934</v>
       </c>
       <c r="E42">
-        <v>0.7519999999999999</v>
+        <v>0.7797999999999999</v>
       </c>
       <c r="F42">
-        <v>1.112</v>
+        <v>1.1398</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4719,28 +4719,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M42">
-        <v>0.05949199999999999</v>
+        <v>0.06097929999999999</v>
       </c>
       <c r="N42">
-        <v>0.4695079999999999</v>
+        <v>0.4680206999999999</v>
       </c>
       <c r="O42">
-        <v>0.07512127999999998</v>
+        <v>0.07488331199999998</v>
       </c>
       <c r="P42">
-        <v>0.39438672</v>
+        <v>0.3931373879999999</v>
       </c>
       <c r="Q42">
-        <v>0.8043867199999999</v>
+        <v>0.8031373879999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1396134869102442</v>
+        <v>0.1410404630257846</v>
       </c>
       <c r="T42">
-        <v>1.291377959183438</v>
+        <v>1.311020822534773</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.89195185907349</v>
+        <v>8.67507498446194</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1016392731852129</v>
+        <v>0.1015344542242793</v>
       </c>
       <c r="C43">
-        <v>1.703277539339934</v>
+        <v>1.676648730949267</v>
       </c>
       <c r="D43">
-        <v>2.843077539339934</v>
+        <v>2.844248730949267</v>
       </c>
       <c r="E43">
-        <v>0.7797999999999999</v>
+        <v>0.8076</v>
       </c>
       <c r="F43">
-        <v>1.1398</v>
+        <v>1.1676</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4801,28 +4801,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M43">
-        <v>0.06097929999999999</v>
+        <v>0.0624666</v>
       </c>
       <c r="N43">
-        <v>0.4680206999999999</v>
+        <v>0.4665333999999999</v>
       </c>
       <c r="O43">
-        <v>0.07488331199999998</v>
+        <v>0.07464534399999999</v>
       </c>
       <c r="P43">
-        <v>0.3931373879999999</v>
+        <v>0.3918880559999999</v>
       </c>
       <c r="Q43">
-        <v>0.8031373879999999</v>
+        <v>0.8018880559999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1410404630257846</v>
+        <v>0.1425166452142747</v>
       </c>
       <c r="T43">
-        <v>1.311020822534773</v>
+        <v>1.33134102600167</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.67507498446194</v>
+        <v>8.46852558006999</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1015344542242793</v>
+        <v>0.1014296352633458</v>
       </c>
       <c r="C44">
-        <v>1.676648730949267</v>
+        <v>1.650020887889345</v>
       </c>
       <c r="D44">
-        <v>2.844248730949267</v>
+        <v>2.845420887889345</v>
       </c>
       <c r="E44">
-        <v>0.8076</v>
+        <v>0.8353999999999998</v>
       </c>
       <c r="F44">
-        <v>1.1676</v>
+        <v>1.1954</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4883,28 +4883,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M44">
-        <v>0.0624666</v>
+        <v>0.06395389999999999</v>
       </c>
       <c r="N44">
-        <v>0.4665333999999999</v>
+        <v>0.4650460999999999</v>
       </c>
       <c r="O44">
-        <v>0.07464534399999999</v>
+        <v>0.07440737599999998</v>
       </c>
       <c r="P44">
-        <v>0.3918880559999999</v>
+        <v>0.3906387239999999</v>
       </c>
       <c r="Q44">
-        <v>0.8018880559999999</v>
+        <v>0.8006387239999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1425166452142747</v>
+        <v>0.1440446232690276</v>
       </c>
       <c r="T44">
-        <v>1.33134102600167</v>
+        <v>1.352374219063898</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.46852558006999</v>
+        <v>8.271583124719523</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1014296352633458</v>
+        <v>0.1013248163024122</v>
       </c>
       <c r="C45">
-        <v>1.650020887889345</v>
+        <v>1.623394011354141</v>
       </c>
       <c r="D45">
-        <v>2.845420887889345</v>
+        <v>2.846594011354141</v>
       </c>
       <c r="E45">
-        <v>0.8353999999999998</v>
+        <v>0.8631999999999999</v>
       </c>
       <c r="F45">
-        <v>1.1954</v>
+        <v>1.2232</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4965,28 +4965,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M45">
-        <v>0.06395389999999999</v>
+        <v>0.06544119999999999</v>
       </c>
       <c r="N45">
-        <v>0.4650460999999999</v>
+        <v>0.4635587999999999</v>
       </c>
       <c r="O45">
-        <v>0.07440737599999998</v>
+        <v>0.07416940799999999</v>
       </c>
       <c r="P45">
-        <v>0.3906387239999999</v>
+        <v>0.3893893919999999</v>
       </c>
       <c r="Q45">
-        <v>0.8006387239999999</v>
+        <v>0.7993893919999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1440446232690276</v>
+        <v>0.1456271719685931</v>
       </c>
       <c r="T45">
-        <v>1.352374219063898</v>
+        <v>1.374158597592633</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.271583124719523</v>
+        <v>8.083592599157718</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1013248163024122</v>
+        <v>0.1012199973414786</v>
       </c>
       <c r="C46">
-        <v>1.623394011354141</v>
+        <v>1.596768102539598</v>
       </c>
       <c r="D46">
-        <v>2.846594011354141</v>
+        <v>2.847768102539598</v>
       </c>
       <c r="E46">
-        <v>0.8631999999999999</v>
+        <v>0.8909999999999999</v>
       </c>
       <c r="F46">
-        <v>1.2232</v>
+        <v>1.251</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5047,28 +5047,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M46">
-        <v>0.06544119999999999</v>
+        <v>0.06692849999999999</v>
       </c>
       <c r="N46">
-        <v>0.4635587999999999</v>
+        <v>0.4620714999999999</v>
       </c>
       <c r="O46">
-        <v>0.07416940799999999</v>
+        <v>0.07393143999999999</v>
       </c>
       <c r="P46">
-        <v>0.3893893919999999</v>
+        <v>0.3881400599999999</v>
       </c>
       <c r="Q46">
-        <v>0.7993893919999999</v>
+        <v>0.7981400599999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1456271719685931</v>
+        <v>0.1472672678935974</v>
       </c>
       <c r="T46">
-        <v>1.374158597592633</v>
+        <v>1.396735135340595</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.083592599157718</v>
+        <v>7.903957208065323</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1012199973414786</v>
+        <v>0.101115178380545</v>
       </c>
       <c r="C47">
-        <v>1.596768102539598</v>
+        <v>1.570143162643634</v>
       </c>
       <c r="D47">
-        <v>2.847768102539598</v>
+        <v>2.848943162643633</v>
       </c>
       <c r="E47">
-        <v>0.8909999999999999</v>
+        <v>0.9188</v>
       </c>
       <c r="F47">
-        <v>1.251</v>
+        <v>1.2788</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5129,28 +5129,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M47">
-        <v>0.06692849999999999</v>
+        <v>0.0684158</v>
       </c>
       <c r="N47">
-        <v>0.4620714999999999</v>
+        <v>0.4605841999999999</v>
       </c>
       <c r="O47">
-        <v>0.07393143999999999</v>
+        <v>0.07369347199999998</v>
       </c>
       <c r="P47">
-        <v>0.3881400599999999</v>
+        <v>0.3868907279999999</v>
       </c>
       <c r="Q47">
-        <v>0.7981400599999999</v>
+        <v>0.7968907279999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1472672678935974</v>
+        <v>0.1489681081121204</v>
       </c>
       <c r="T47">
-        <v>1.396735135340595</v>
+        <v>1.420147841153297</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.903957208065323</v>
+        <v>7.73213205136825</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.101115178380545</v>
+        <v>0.1013261994196114</v>
       </c>
       <c r="C48">
-        <v>1.570143162643634</v>
+        <v>1.539978525345165</v>
       </c>
       <c r="D48">
-        <v>2.848943162643633</v>
+        <v>2.846578525345165</v>
       </c>
       <c r="E48">
-        <v>0.9188</v>
+        <v>0.9466</v>
       </c>
       <c r="F48">
-        <v>1.2788</v>
+        <v>1.3066</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5211,45 +5211,45 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M48">
-        <v>0.0684158</v>
+        <v>0.07094838000000001</v>
       </c>
       <c r="N48">
-        <v>0.4605841999999999</v>
+        <v>0.4580516199999999</v>
       </c>
       <c r="O48">
-        <v>0.07369347199999998</v>
+        <v>0.07328825919999998</v>
       </c>
       <c r="P48">
-        <v>0.3868907279999999</v>
+        <v>0.3847633607999999</v>
       </c>
       <c r="Q48">
-        <v>0.7968907279999999</v>
+        <v>0.7947633607999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1489681081121204</v>
+        <v>0.1507331309803989</v>
       </c>
       <c r="T48">
-        <v>1.420147841153297</v>
+        <v>1.444444045298553</v>
       </c>
       <c r="U48">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V48">
         <v>0.16</v>
       </c>
       <c r="W48">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y48">
-        <v>7.73213205136825</v>
+        <v>7.456125143378888</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1013261994196114</v>
+        <v>0.1012281004586778</v>
       </c>
       <c r="C49">
-        <v>1.539978525345165</v>
+        <v>1.513277303900302</v>
       </c>
       <c r="D49">
-        <v>2.846578525345165</v>
+        <v>2.847677303900302</v>
       </c>
       <c r="E49">
-        <v>0.9466</v>
+        <v>0.9744</v>
       </c>
       <c r="F49">
-        <v>1.3066</v>
+        <v>1.3344</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5293,28 +5293,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M49">
-        <v>0.07094838000000001</v>
+        <v>0.07245792000000001</v>
       </c>
       <c r="N49">
-        <v>0.4580516199999999</v>
+        <v>0.4565420799999999</v>
       </c>
       <c r="O49">
-        <v>0.07328825919999998</v>
+        <v>0.07304673279999999</v>
       </c>
       <c r="P49">
-        <v>0.3847633607999999</v>
+        <v>0.3834953471999999</v>
       </c>
       <c r="Q49">
-        <v>0.7947633607999999</v>
+        <v>0.7934953471999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1507331309803989</v>
+        <v>0.1525660393436112</v>
       </c>
       <c r="T49">
-        <v>1.444444045298553</v>
+        <v>1.469674718834012</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.456125143378888</v>
+        <v>7.300789202891828</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1012281004586778</v>
+        <v>0.1011300014977443</v>
       </c>
       <c r="C50">
-        <v>1.513277303900302</v>
+        <v>1.486576931039454</v>
       </c>
       <c r="D50">
-        <v>2.847677303900302</v>
+        <v>2.848776931039454</v>
       </c>
       <c r="E50">
-        <v>0.9743999999999998</v>
+        <v>1.0022</v>
       </c>
       <c r="F50">
-        <v>1.3344</v>
+        <v>1.3622</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5375,28 +5375,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M50">
-        <v>0.07245792</v>
+        <v>0.07396746</v>
       </c>
       <c r="N50">
-        <v>0.4565420799999999</v>
+        <v>0.4550325399999999</v>
       </c>
       <c r="O50">
-        <v>0.07304673279999999</v>
+        <v>0.07280520639999999</v>
       </c>
       <c r="P50">
-        <v>0.3834953471999999</v>
+        <v>0.3822273335999999</v>
       </c>
       <c r="Q50">
-        <v>0.7934953471999999</v>
+        <v>0.7922273335999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1525660393436112</v>
+        <v>0.1544708264661652</v>
       </c>
       <c r="T50">
-        <v>1.469674718834012</v>
+        <v>1.495894830547331</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.30078920289183</v>
+        <v>7.151793504873629</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1011300014977443</v>
+        <v>0.1010319025368107</v>
       </c>
       <c r="C51">
-        <v>1.486576931039454</v>
+        <v>1.459877407746039</v>
       </c>
       <c r="D51">
-        <v>2.848776931039454</v>
+        <v>2.849877407746039</v>
       </c>
       <c r="E51">
-        <v>1.0022</v>
+        <v>1.03</v>
       </c>
       <c r="F51">
-        <v>1.3622</v>
+        <v>1.39</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5457,28 +5457,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M51">
-        <v>0.07396746</v>
+        <v>0.075477</v>
       </c>
       <c r="N51">
-        <v>0.4550325399999999</v>
+        <v>0.4535229999999999</v>
       </c>
       <c r="O51">
-        <v>0.07280520639999999</v>
+        <v>0.07256367999999999</v>
       </c>
       <c r="P51">
-        <v>0.3822273335999999</v>
+        <v>0.3809593199999999</v>
       </c>
       <c r="Q51">
-        <v>0.7922273335999999</v>
+        <v>0.7909593199999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1544708264661652</v>
+        <v>0.1564518050736213</v>
       </c>
       <c r="T51">
-        <v>1.495894830547331</v>
+        <v>1.523163746729184</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.151793504873629</v>
+        <v>7.008757634776155</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1010319025368107</v>
+        <v>0.1009338035758771</v>
       </c>
       <c r="C52">
-        <v>1.459877407746039</v>
+        <v>1.433178735004996</v>
       </c>
       <c r="D52">
-        <v>2.849877407746039</v>
+        <v>2.850978735004996</v>
       </c>
       <c r="E52">
-        <v>1.03</v>
+        <v>1.0578</v>
       </c>
       <c r="F52">
-        <v>1.39</v>
+        <v>1.4178</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5539,28 +5539,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M52">
-        <v>0.075477</v>
+        <v>0.07698653999999999</v>
       </c>
       <c r="N52">
-        <v>0.4535229999999999</v>
+        <v>0.4520134599999999</v>
       </c>
       <c r="O52">
-        <v>0.07256367999999999</v>
+        <v>0.07232215359999999</v>
       </c>
       <c r="P52">
-        <v>0.3809593199999999</v>
+        <v>0.3796913063999999</v>
       </c>
       <c r="Q52">
-        <v>0.7909593199999998</v>
+        <v>0.7896913064</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1564518050736213</v>
+        <v>0.1585136399507696</v>
       </c>
       <c r="T52">
-        <v>1.523163746729184</v>
+        <v>1.551545679898051</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.008757634776155</v>
+        <v>6.871331014486428</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1009338035758771</v>
+        <v>0.1008357046149435</v>
       </c>
       <c r="C53">
-        <v>1.433178735004996</v>
+        <v>1.406480913802788</v>
       </c>
       <c r="D53">
-        <v>2.850978735004996</v>
+        <v>2.852080913802788</v>
       </c>
       <c r="E53">
-        <v>1.0578</v>
+        <v>1.0856</v>
       </c>
       <c r="F53">
-        <v>1.4178</v>
+        <v>1.4456</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5621,28 +5621,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M53">
-        <v>0.07698653999999999</v>
+        <v>0.07849608</v>
       </c>
       <c r="N53">
-        <v>0.4520134599999999</v>
+        <v>0.4505039199999999</v>
       </c>
       <c r="O53">
-        <v>0.07232215359999999</v>
+        <v>0.0720806272</v>
       </c>
       <c r="P53">
-        <v>0.3796913063999999</v>
+        <v>0.3784232928</v>
       </c>
       <c r="Q53">
-        <v>0.7896913064</v>
+        <v>0.7884232927999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1585136399507696</v>
+        <v>0.1606613846144656</v>
       </c>
       <c r="T53">
-        <v>1.551545679898051</v>
+        <v>1.58111019361562</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.871331014486428</v>
+        <v>6.739190033438612</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1008357046149435</v>
+        <v>0.1007376056540099</v>
       </c>
       <c r="C54">
-        <v>1.406480913802788</v>
+        <v>1.379783945127402</v>
       </c>
       <c r="D54">
-        <v>2.852080913802788</v>
+        <v>2.853183945127402</v>
       </c>
       <c r="E54">
-        <v>1.0856</v>
+        <v>1.1134</v>
       </c>
       <c r="F54">
-        <v>1.4456</v>
+        <v>1.4734</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5703,28 +5703,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M54">
-        <v>0.07849608</v>
+        <v>0.08000562</v>
       </c>
       <c r="N54">
-        <v>0.4505039199999999</v>
+        <v>0.4489943799999999</v>
       </c>
       <c r="O54">
-        <v>0.0720806272</v>
+        <v>0.07183910079999999</v>
       </c>
       <c r="P54">
-        <v>0.3784232928</v>
+        <v>0.3771552791999999</v>
       </c>
       <c r="Q54">
-        <v>0.7884232927999999</v>
+        <v>0.7871552791999998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1606613846144656</v>
+        <v>0.1629005226681062</v>
       </c>
       <c r="T54">
-        <v>1.58111019361562</v>
+        <v>1.611932771746703</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.739190033438612</v>
+        <v>6.612035504505807</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1007376056540099</v>
+        <v>0.1006395066930763</v>
       </c>
       <c r="C55">
-        <v>1.379783945127402</v>
+        <v>1.353087829968356</v>
       </c>
       <c r="D55">
-        <v>2.853183945127402</v>
+        <v>2.854287829968356</v>
       </c>
       <c r="E55">
-        <v>1.1134</v>
+        <v>1.1412</v>
       </c>
       <c r="F55">
-        <v>1.4734</v>
+        <v>1.5012</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5785,28 +5785,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M55">
-        <v>0.08000562</v>
+        <v>0.08151516</v>
       </c>
       <c r="N55">
-        <v>0.4489943799999999</v>
+        <v>0.4474848399999999</v>
       </c>
       <c r="O55">
-        <v>0.07183910079999999</v>
+        <v>0.07159757439999999</v>
       </c>
       <c r="P55">
-        <v>0.3771552791999999</v>
+        <v>0.3758872655999999</v>
       </c>
       <c r="Q55">
-        <v>0.7871552791999998</v>
+        <v>0.7858872655999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1629005226681062</v>
+        <v>0.1652370145501659</v>
       </c>
       <c r="T55">
-        <v>1.611932771746703</v>
+        <v>1.644095461970442</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.612035504505807</v>
+        <v>6.489590402570514</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1006395066930763</v>
+        <v>0.1005414077321427</v>
       </c>
       <c r="C56">
-        <v>1.353087829968356</v>
+        <v>1.326392569316698</v>
       </c>
       <c r="D56">
-        <v>2.854287829968356</v>
+        <v>2.855392569316697</v>
       </c>
       <c r="E56">
-        <v>1.1412</v>
+        <v>1.169</v>
       </c>
       <c r="F56">
-        <v>1.5012</v>
+        <v>1.529</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5867,28 +5867,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M56">
-        <v>0.08151516</v>
+        <v>0.08302469999999999</v>
       </c>
       <c r="N56">
-        <v>0.4474848399999999</v>
+        <v>0.4459752999999999</v>
       </c>
       <c r="O56">
-        <v>0.07159757439999999</v>
+        <v>0.07135604799999999</v>
       </c>
       <c r="P56">
-        <v>0.3758872655999999</v>
+        <v>0.3746192519999999</v>
       </c>
       <c r="Q56">
-        <v>0.7858872655999999</v>
+        <v>0.7846192519999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1652370145501659</v>
+        <v>0.1676773505158728</v>
       </c>
       <c r="T56">
-        <v>1.644095461970442</v>
+        <v>1.677687605093014</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.489590402570514</v>
+        <v>6.371597849796506</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1005414077321427</v>
+        <v>0.1004433087712092</v>
       </c>
       <c r="C57">
-        <v>1.326392569316698</v>
+        <v>1.299698164165012</v>
       </c>
       <c r="D57">
-        <v>2.855392569316697</v>
+        <v>2.856498164165012</v>
       </c>
       <c r="E57">
-        <v>1.169</v>
+        <v>1.1968</v>
       </c>
       <c r="F57">
-        <v>1.529</v>
+        <v>1.5568</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5949,28 +5949,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M57">
-        <v>0.08302469999999999</v>
+        <v>0.08453424</v>
       </c>
       <c r="N57">
-        <v>0.4459752999999999</v>
+        <v>0.4444657599999999</v>
       </c>
       <c r="O57">
-        <v>0.07135604799999999</v>
+        <v>0.07111452159999999</v>
       </c>
       <c r="P57">
-        <v>0.3746192519999999</v>
+        <v>0.3733512384</v>
       </c>
       <c r="Q57">
-        <v>0.7846192519999999</v>
+        <v>0.7833512383999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1676773505158728</v>
+        <v>0.1702286108436572</v>
       </c>
       <c r="T57">
-        <v>1.677687605093014</v>
+        <v>1.712806663812066</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.371597849796506</v>
+        <v>6.257819316764425</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1004433087712092</v>
+        <v>0.1003452098102756</v>
       </c>
       <c r="C58">
-        <v>1.299698164165012</v>
+        <v>1.27300461550742</v>
       </c>
       <c r="D58">
-        <v>2.856498164165012</v>
+        <v>2.85760461550742</v>
       </c>
       <c r="E58">
-        <v>1.1968</v>
+        <v>1.2246</v>
       </c>
       <c r="F58">
-        <v>1.5568</v>
+        <v>1.5846</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6031,28 +6031,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M58">
-        <v>0.08453424</v>
+        <v>0.08604378</v>
       </c>
       <c r="N58">
-        <v>0.4444657599999999</v>
+        <v>0.4429562199999999</v>
       </c>
       <c r="O58">
-        <v>0.07111452159999999</v>
+        <v>0.07087299519999998</v>
       </c>
       <c r="P58">
-        <v>0.3733512384</v>
+        <v>0.3720832247999999</v>
       </c>
       <c r="Q58">
-        <v>0.7833512383999999</v>
+        <v>0.7820832247999998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1702286108436572</v>
+        <v>0.1728985344425014</v>
       </c>
       <c r="T58">
-        <v>1.712806663812066</v>
+        <v>1.749559167122703</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.257819316764425</v>
+        <v>6.14803301296154</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1003452098102756</v>
+        <v>0.100734310849342</v>
       </c>
       <c r="C59">
-        <v>1.27300461550742</v>
+        <v>1.240821006942224</v>
       </c>
       <c r="D59">
-        <v>2.85760461550742</v>
+        <v>2.853221006942224</v>
       </c>
       <c r="E59">
-        <v>1.2246</v>
+        <v>1.2524</v>
       </c>
       <c r="F59">
-        <v>1.5846</v>
+        <v>1.6124</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6113,45 +6113,45 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M59">
-        <v>0.08604378</v>
+        <v>0.08916572</v>
       </c>
       <c r="N59">
-        <v>0.4429562199999999</v>
+        <v>0.4398342799999999</v>
       </c>
       <c r="O59">
-        <v>0.07087299519999998</v>
+        <v>0.07037348479999998</v>
       </c>
       <c r="P59">
-        <v>0.3720832247999999</v>
+        <v>0.3694607951999999</v>
       </c>
       <c r="Q59">
-        <v>0.7820832247999998</v>
+        <v>0.7794607951999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1728985344425014</v>
+        <v>0.1756955972603381</v>
       </c>
       <c r="T59">
-        <v>1.749559167122703</v>
+        <v>1.788061789638607</v>
       </c>
       <c r="U59">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V59">
         <v>0.16</v>
       </c>
       <c r="W59">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>6.14803301296154</v>
+        <v>5.932773267574129</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.100734310849342</v>
+        <v>0.1006446118884084</v>
       </c>
       <c r="C60">
-        <v>1.240821006942224</v>
+        <v>1.214030361320958</v>
       </c>
       <c r="D60">
-        <v>2.853221006942224</v>
+        <v>2.854230361320957</v>
       </c>
       <c r="E60">
-        <v>1.2524</v>
+        <v>1.2802</v>
       </c>
       <c r="F60">
-        <v>1.6124</v>
+        <v>1.6402</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6195,28 +6195,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M60">
-        <v>0.08916571999999999</v>
+        <v>0.09070306</v>
       </c>
       <c r="N60">
-        <v>0.4398342799999999</v>
+        <v>0.4382969399999999</v>
       </c>
       <c r="O60">
-        <v>0.07037348479999998</v>
+        <v>0.07012751039999998</v>
       </c>
       <c r="P60">
-        <v>0.3694607951999999</v>
+        <v>0.3681694295999999</v>
       </c>
       <c r="Q60">
-        <v>0.7794607951999999</v>
+        <v>0.7781694295999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1756955972603381</v>
+        <v>0.1786291021668498</v>
       </c>
       <c r="T60">
-        <v>1.788061789638607</v>
+        <v>1.828442588862604</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.93277326757413</v>
+        <v>5.832217788462703</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1006446118884084</v>
+        <v>0.1005549129274748</v>
       </c>
       <c r="C61">
-        <v>1.214030361320958</v>
+        <v>1.187240430090055</v>
       </c>
       <c r="D61">
-        <v>2.854230361320957</v>
+        <v>2.855240430090055</v>
       </c>
       <c r="E61">
-        <v>1.2802</v>
+        <v>1.308</v>
       </c>
       <c r="F61">
-        <v>1.6402</v>
+        <v>1.668</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6277,28 +6277,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M61">
-        <v>0.09070306</v>
+        <v>0.0922404</v>
       </c>
       <c r="N61">
-        <v>0.4382969399999999</v>
+        <v>0.4367595999999999</v>
       </c>
       <c r="O61">
-        <v>0.07012751039999998</v>
+        <v>0.06988153599999999</v>
       </c>
       <c r="P61">
-        <v>0.3681694295999999</v>
+        <v>0.3668780639999999</v>
       </c>
       <c r="Q61">
-        <v>0.7781694295999999</v>
+        <v>0.7768780639999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1786291021668498</v>
+        <v>0.1817092823186871</v>
       </c>
       <c r="T61">
-        <v>1.828442588862604</v>
+        <v>1.870842428047802</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.832217788462703</v>
+        <v>5.735014158654992</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1005549129274748</v>
+        <v>0.1004652139665412</v>
       </c>
       <c r="C62">
-        <v>1.187240430090055</v>
+        <v>1.160451214008224</v>
       </c>
       <c r="D62">
-        <v>2.855240430090055</v>
+        <v>2.856251214008223</v>
       </c>
       <c r="E62">
-        <v>1.308</v>
+        <v>1.3358</v>
       </c>
       <c r="F62">
-        <v>1.668</v>
+        <v>1.6958</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6359,28 +6359,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M62">
-        <v>0.0922404</v>
+        <v>0.09377773999999998</v>
       </c>
       <c r="N62">
-        <v>0.4367595999999999</v>
+        <v>0.4352222599999999</v>
       </c>
       <c r="O62">
-        <v>0.06988153599999999</v>
+        <v>0.06963556159999999</v>
       </c>
       <c r="P62">
-        <v>0.3668780639999999</v>
+        <v>0.3655866983999999</v>
       </c>
       <c r="Q62">
-        <v>0.7768780639999999</v>
+        <v>0.7755866983999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1817092823186871</v>
+        <v>0.1849474204270288</v>
       </c>
       <c r="T62">
-        <v>1.870842428047802</v>
+        <v>1.915416617960445</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.735014158654992</v>
+        <v>5.640997533103271</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1004652139665412</v>
+        <v>0.1003755150056077</v>
       </c>
       <c r="C63">
-        <v>1.160451214008224</v>
+        <v>1.13366271383524</v>
       </c>
       <c r="D63">
-        <v>2.856251214008223</v>
+        <v>2.857262713835239</v>
       </c>
       <c r="E63">
-        <v>1.3358</v>
+        <v>1.3636</v>
       </c>
       <c r="F63">
-        <v>1.6958</v>
+        <v>1.7236</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6441,28 +6441,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M63">
-        <v>0.09377773999999998</v>
+        <v>0.09531508</v>
       </c>
       <c r="N63">
-        <v>0.4352222599999999</v>
+        <v>0.4336849199999999</v>
       </c>
       <c r="O63">
-        <v>0.06963556159999999</v>
+        <v>0.06938958719999999</v>
       </c>
       <c r="P63">
-        <v>0.3655866983999999</v>
+        <v>0.3642953327999999</v>
       </c>
       <c r="Q63">
-        <v>0.7755866983999999</v>
+        <v>0.7742953328</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1849474204270288</v>
+        <v>0.1883559868568623</v>
       </c>
       <c r="T63">
-        <v>1.915416617960445</v>
+        <v>1.962336817868491</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.640997533103271</v>
+        <v>5.550013701924186</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1003755150056077</v>
+        <v>0.1002858160446741</v>
       </c>
       <c r="C64">
-        <v>1.13366271383524</v>
+        <v>1.106874930331959</v>
       </c>
       <c r="D64">
-        <v>2.857262713835239</v>
+        <v>2.858274930331959</v>
       </c>
       <c r="E64">
-        <v>1.3636</v>
+        <v>1.3914</v>
       </c>
       <c r="F64">
-        <v>1.7236</v>
+        <v>1.7514</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6523,28 +6523,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M64">
-        <v>0.09531508</v>
+        <v>0.09685241999999999</v>
       </c>
       <c r="N64">
-        <v>0.4336849199999999</v>
+        <v>0.4321475799999999</v>
       </c>
       <c r="O64">
-        <v>0.06938958719999999</v>
+        <v>0.06914361279999999</v>
       </c>
       <c r="P64">
-        <v>0.3642953327999999</v>
+        <v>0.3630039671999999</v>
       </c>
       <c r="Q64">
-        <v>0.7742953328</v>
+        <v>0.7730039672</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1883559868568623</v>
+        <v>0.1919488001207408</v>
       </c>
       <c r="T64">
-        <v>1.962336817868491</v>
+        <v>2.011793244798593</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.550013701924186</v>
+        <v>5.461918246338088</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1002858160446741</v>
+        <v>0.1001961170837405</v>
       </c>
       <c r="C65">
-        <v>1.106874930331959</v>
+        <v>1.080087864260317</v>
       </c>
       <c r="D65">
-        <v>2.858274930331959</v>
+        <v>2.859287864260317</v>
       </c>
       <c r="E65">
-        <v>1.3914</v>
+        <v>1.4192</v>
       </c>
       <c r="F65">
-        <v>1.7514</v>
+        <v>1.7792</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6605,28 +6605,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M65">
-        <v>0.09685241999999999</v>
+        <v>0.09838975999999999</v>
       </c>
       <c r="N65">
-        <v>0.4321475799999999</v>
+        <v>0.4306102399999999</v>
       </c>
       <c r="O65">
-        <v>0.06914361279999999</v>
+        <v>0.06889763839999999</v>
       </c>
       <c r="P65">
-        <v>0.3630039671999999</v>
+        <v>0.3617126016</v>
       </c>
       <c r="Q65">
-        <v>0.7730039672</v>
+        <v>0.7717126016</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1919488001207408</v>
+        <v>0.1957412141215014</v>
       </c>
       <c r="T65">
-        <v>2.011793244798593</v>
+        <v>2.063997251002589</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.461918246338088</v>
+        <v>5.376575773739055</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1001961170837405</v>
+        <v>0.1001064181228069</v>
       </c>
       <c r="C66">
-        <v>1.080087864260317</v>
+        <v>1.053301516383327</v>
       </c>
       <c r="D66">
-        <v>2.859287864260317</v>
+        <v>2.860301516383327</v>
       </c>
       <c r="E66">
-        <v>1.4192</v>
+        <v>1.447</v>
       </c>
       <c r="F66">
-        <v>1.7792</v>
+        <v>1.807</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6687,28 +6687,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M66">
-        <v>0.09838975999999999</v>
+        <v>0.0999271</v>
       </c>
       <c r="N66">
-        <v>0.4306102399999999</v>
+        <v>0.4290728999999999</v>
       </c>
       <c r="O66">
-        <v>0.06889763839999999</v>
+        <v>0.06865166399999999</v>
       </c>
       <c r="P66">
-        <v>0.3617126016</v>
+        <v>0.3604212359999999</v>
       </c>
       <c r="Q66">
-        <v>0.7717126016</v>
+        <v>0.7704212359999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1957412141215014</v>
+        <v>0.1997503374937341</v>
       </c>
       <c r="T66">
-        <v>2.063997251002589</v>
+        <v>2.119184343275387</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.376575773739055</v>
+        <v>5.293859223373839</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1001064181228069</v>
+        <v>0.1000167191618733</v>
       </c>
       <c r="C67">
-        <v>1.053301516383327</v>
+        <v>1.026515887465086</v>
       </c>
       <c r="D67">
-        <v>2.860301516383327</v>
+        <v>2.861315887465086</v>
       </c>
       <c r="E67">
-        <v>1.447</v>
+        <v>1.4748</v>
       </c>
       <c r="F67">
-        <v>1.807</v>
+        <v>1.8348</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6769,28 +6769,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M67">
-        <v>0.0999271</v>
+        <v>0.10146444</v>
       </c>
       <c r="N67">
-        <v>0.4290728999999999</v>
+        <v>0.4275355599999999</v>
       </c>
       <c r="O67">
-        <v>0.06865166399999999</v>
+        <v>0.06840568959999999</v>
       </c>
       <c r="P67">
-        <v>0.3604212359999999</v>
+        <v>0.3591298703999999</v>
       </c>
       <c r="Q67">
-        <v>0.7704212359999999</v>
+        <v>0.7691298703999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1997503374937341</v>
+        <v>0.2039952916525686</v>
       </c>
       <c r="T67">
-        <v>2.119184343275387</v>
+        <v>2.177617735093642</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.293859223373839</v>
+        <v>5.213649235140902</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1000167191618733</v>
+        <v>0.09992702020093974</v>
       </c>
       <c r="C68">
-        <v>1.026515887465086</v>
+        <v>0.9997309782707764</v>
       </c>
       <c r="D68">
-        <v>2.861315887465086</v>
+        <v>2.862330978270776</v>
       </c>
       <c r="E68">
-        <v>1.4748</v>
+        <v>1.5026</v>
       </c>
       <c r="F68">
-        <v>1.8348</v>
+        <v>1.8626</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6851,28 +6851,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M68">
-        <v>0.10146444</v>
+        <v>0.10300178</v>
       </c>
       <c r="N68">
-        <v>0.4275355599999999</v>
+        <v>0.4259982199999999</v>
       </c>
       <c r="O68">
-        <v>0.06840568959999999</v>
+        <v>0.06815971519999998</v>
       </c>
       <c r="P68">
-        <v>0.3591298703999999</v>
+        <v>0.3578385048</v>
       </c>
       <c r="Q68">
-        <v>0.7691298703999999</v>
+        <v>0.7678385047999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2039952916525686</v>
+        <v>0.2084975157604235</v>
       </c>
       <c r="T68">
-        <v>2.177617735093642</v>
+        <v>2.239592544597852</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.213649235140902</v>
+        <v>5.135833574914918</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09992702020093974</v>
+        <v>0.09983732124000616</v>
       </c>
       <c r="C69">
-        <v>0.9997309782707764</v>
+        <v>0.9729467895666644</v>
       </c>
       <c r="D69">
-        <v>2.862330978270776</v>
+        <v>2.863346789566664</v>
       </c>
       <c r="E69">
-        <v>1.5026</v>
+        <v>1.5304</v>
       </c>
       <c r="F69">
-        <v>1.8626</v>
+        <v>1.8904</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6933,28 +6933,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M69">
-        <v>0.10300178</v>
+        <v>0.10453912</v>
       </c>
       <c r="N69">
-        <v>0.4259982199999999</v>
+        <v>0.4244608799999999</v>
       </c>
       <c r="O69">
-        <v>0.06815971519999998</v>
+        <v>0.0679137408</v>
       </c>
       <c r="P69">
-        <v>0.3578385048</v>
+        <v>0.3565471391999999</v>
       </c>
       <c r="Q69">
-        <v>0.7678385047999999</v>
+        <v>0.7665471391999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2084975157604235</v>
+        <v>0.2132811288750193</v>
       </c>
       <c r="T69">
-        <v>2.239592544597852</v>
+        <v>2.305440779696075</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.135833574914918</v>
+        <v>5.060306610577934</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09983732124000616</v>
+        <v>0.09974762227907258</v>
       </c>
       <c r="C70">
-        <v>0.9729467895666644</v>
+        <v>0.946163322120106</v>
       </c>
       <c r="D70">
-        <v>2.863346789566664</v>
+        <v>2.864363322120106</v>
       </c>
       <c r="E70">
-        <v>1.5304</v>
+        <v>1.5582</v>
       </c>
       <c r="F70">
-        <v>1.8904</v>
+        <v>1.9182</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7015,28 +7015,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M70">
-        <v>0.10453912</v>
+        <v>0.10607646</v>
       </c>
       <c r="N70">
-        <v>0.4244608799999999</v>
+        <v>0.4229235399999999</v>
       </c>
       <c r="O70">
-        <v>0.0679137408</v>
+        <v>0.06766776639999998</v>
       </c>
       <c r="P70">
-        <v>0.3565471391999999</v>
+        <v>0.3552557735999999</v>
       </c>
       <c r="Q70">
-        <v>0.7665471391999998</v>
+        <v>0.7652557735999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2132811288750193</v>
+        <v>0.2183733621905567</v>
       </c>
       <c r="T70">
-        <v>2.305440779696075</v>
+        <v>2.375537288026441</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.060306610577934</v>
+        <v>4.986968833613036</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09974762227907258</v>
+        <v>0.099657923318139</v>
       </c>
       <c r="C71">
-        <v>0.946163322120106</v>
+        <v>0.9193805766995478</v>
       </c>
       <c r="D71">
-        <v>2.864363322120106</v>
+        <v>2.865380576699548</v>
       </c>
       <c r="E71">
-        <v>1.5582</v>
+        <v>1.586</v>
       </c>
       <c r="F71">
-        <v>1.9182</v>
+        <v>1.946</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7097,28 +7097,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M71">
-        <v>0.10607646</v>
+        <v>0.1076138</v>
       </c>
       <c r="N71">
-        <v>0.4229235399999999</v>
+        <v>0.4213861999999999</v>
       </c>
       <c r="O71">
-        <v>0.06766776639999998</v>
+        <v>0.06742179199999999</v>
       </c>
       <c r="P71">
-        <v>0.3552557735999999</v>
+        <v>0.353964408</v>
       </c>
       <c r="Q71">
-        <v>0.7652557735999999</v>
+        <v>0.7639644079999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2183733621905567</v>
+        <v>0.22380507772713</v>
       </c>
       <c r="T71">
-        <v>2.375537288026441</v>
+        <v>2.450306896912166</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.986968833613036</v>
+        <v>4.91572642170428</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.099657923318139</v>
+        <v>0.09956822435720541</v>
       </c>
       <c r="C72">
-        <v>0.9193805766995478</v>
+        <v>0.892598554074526</v>
       </c>
       <c r="D72">
-        <v>2.865380576699548</v>
+        <v>2.866398554074526</v>
       </c>
       <c r="E72">
-        <v>1.586</v>
+        <v>1.6138</v>
       </c>
       <c r="F72">
-        <v>1.946</v>
+        <v>1.9738</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7179,28 +7179,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M72">
-        <v>0.1076138</v>
+        <v>0.10915114</v>
       </c>
       <c r="N72">
-        <v>0.4213861999999999</v>
+        <v>0.4198488599999999</v>
       </c>
       <c r="O72">
-        <v>0.06742179199999999</v>
+        <v>0.06717581759999998</v>
       </c>
       <c r="P72">
-        <v>0.353964408</v>
+        <v>0.3526730423999999</v>
       </c>
       <c r="Q72">
-        <v>0.7639644079999999</v>
+        <v>0.7626730423999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.22380507772713</v>
+        <v>0.2296113943351911</v>
       </c>
       <c r="T72">
-        <v>2.450306896912166</v>
+        <v>2.53023303054863</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.91572642170428</v>
+        <v>4.846490838299992</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0995682243572054</v>
+        <v>0.09947852539627183</v>
       </c>
       <c r="C73">
-        <v>0.8925985540745263</v>
+        <v>0.8658172550156733</v>
       </c>
       <c r="D73">
-        <v>2.866398554074526</v>
+        <v>2.867417255015673</v>
       </c>
       <c r="E73">
-        <v>1.6138</v>
+        <v>1.6416</v>
       </c>
       <c r="F73">
-        <v>1.9738</v>
+        <v>2.0016</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7261,28 +7261,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M73">
-        <v>0.10915114</v>
+        <v>0.11068848</v>
       </c>
       <c r="N73">
-        <v>0.4198488599999999</v>
+        <v>0.4183115199999999</v>
       </c>
       <c r="O73">
-        <v>0.06717581759999999</v>
+        <v>0.06692984319999999</v>
       </c>
       <c r="P73">
-        <v>0.3526730424</v>
+        <v>0.3513816767999999</v>
       </c>
       <c r="Q73">
-        <v>0.7626730423999999</v>
+        <v>0.7613816767999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.229611394335191</v>
+        <v>0.2358324478438279</v>
       </c>
       <c r="T73">
-        <v>2.530233030548629</v>
+        <v>2.615868173730555</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.846490838299994</v>
+        <v>4.779178465545828</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09947852539627183</v>
+        <v>0.09938882643533822</v>
       </c>
       <c r="C74">
-        <v>0.8658172550156733</v>
+        <v>0.8390366802947162</v>
       </c>
       <c r="D74">
-        <v>2.867417255015673</v>
+        <v>2.868436680294716</v>
       </c>
       <c r="E74">
-        <v>1.6416</v>
+        <v>1.6694</v>
       </c>
       <c r="F74">
-        <v>2.0016</v>
+        <v>2.0294</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7343,28 +7343,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M74">
-        <v>0.11068848</v>
+        <v>0.11222582</v>
       </c>
       <c r="N74">
-        <v>0.4183115199999999</v>
+        <v>0.4167741799999999</v>
       </c>
       <c r="O74">
-        <v>0.06692984319999999</v>
+        <v>0.06668386879999999</v>
       </c>
       <c r="P74">
-        <v>0.3513816767999999</v>
+        <v>0.3500903111999999</v>
       </c>
       <c r="Q74">
-        <v>0.7613816767999999</v>
+        <v>0.7600903111999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2358324478438279</v>
+        <v>0.2425143201308823</v>
       </c>
       <c r="T74">
-        <v>2.615868173730555</v>
+        <v>2.707846660851882</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.779178465545828</v>
+        <v>4.713710267387665</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09938882643533822</v>
+        <v>0.09929912747440466</v>
       </c>
       <c r="C75">
-        <v>0.8390366802947162</v>
+        <v>0.8122568306844813</v>
       </c>
       <c r="D75">
-        <v>2.868436680294716</v>
+        <v>2.869456830684481</v>
       </c>
       <c r="E75">
-        <v>1.6694</v>
+        <v>1.6972</v>
       </c>
       <c r="F75">
-        <v>2.0294</v>
+        <v>2.0572</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7425,28 +7425,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M75">
-        <v>0.11222582</v>
+        <v>0.11376316</v>
       </c>
       <c r="N75">
-        <v>0.4167741799999999</v>
+        <v>0.4152368399999999</v>
       </c>
       <c r="O75">
-        <v>0.06668386879999999</v>
+        <v>0.06643789439999999</v>
       </c>
       <c r="P75">
-        <v>0.3500903111999999</v>
+        <v>0.3487989456</v>
       </c>
       <c r="Q75">
-        <v>0.7600903111999999</v>
+        <v>0.7587989455999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2425143201308823</v>
+        <v>0.2497101825938641</v>
       </c>
       <c r="T75">
-        <v>2.707846660851882</v>
+        <v>2.806900416213312</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.713710267387665</v>
+        <v>4.650011479990534</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09929912747440466</v>
+        <v>0.09920942851347106</v>
       </c>
       <c r="C76">
-        <v>0.8122568306844813</v>
+        <v>0.7854777069588939</v>
       </c>
       <c r="D76">
-        <v>2.869456830684481</v>
+        <v>2.870477706958894</v>
       </c>
       <c r="E76">
-        <v>1.6972</v>
+        <v>1.725</v>
       </c>
       <c r="F76">
-        <v>2.0572</v>
+        <v>2.085</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7507,28 +7507,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M76">
-        <v>0.11376316</v>
+        <v>0.1153005</v>
       </c>
       <c r="N76">
-        <v>0.4152368399999999</v>
+        <v>0.4136994999999999</v>
       </c>
       <c r="O76">
-        <v>0.06643789439999999</v>
+        <v>0.06619191999999999</v>
       </c>
       <c r="P76">
-        <v>0.3487989456</v>
+        <v>0.3475075799999999</v>
       </c>
       <c r="Q76">
-        <v>0.7587989455999999</v>
+        <v>0.75750758</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2497101825938641</v>
+        <v>0.2574817140538843</v>
       </c>
       <c r="T76">
-        <v>2.806900416213312</v>
+        <v>2.913878472003656</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.650011479990534</v>
+        <v>4.588011326923993</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09920942851347106</v>
+        <v>0.09911972955253748</v>
       </c>
       <c r="C77">
-        <v>0.7854777069588939</v>
+        <v>0.7586993098929797</v>
       </c>
       <c r="D77">
-        <v>2.870477706958894</v>
+        <v>2.87149930989298</v>
       </c>
       <c r="E77">
-        <v>1.725</v>
+        <v>1.7528</v>
       </c>
       <c r="F77">
-        <v>2.085</v>
+        <v>2.1128</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7589,28 +7589,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M77">
-        <v>0.1153005</v>
+        <v>0.11683784</v>
       </c>
       <c r="N77">
-        <v>0.4136994999999999</v>
+        <v>0.4121621599999999</v>
       </c>
       <c r="O77">
-        <v>0.06619191999999999</v>
+        <v>0.06594594559999999</v>
       </c>
       <c r="P77">
-        <v>0.3475075799999999</v>
+        <v>0.3462162143999999</v>
       </c>
       <c r="Q77">
-        <v>0.75750758</v>
+        <v>0.7562162144</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2574817140538843</v>
+        <v>0.2659008731355729</v>
       </c>
       <c r="T77">
-        <v>2.913878472003656</v>
+        <v>3.029771365776529</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.588011326923993</v>
+        <v>4.527642756832888</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09911972955253748</v>
+        <v>0.1006470305916039</v>
       </c>
       <c r="C78">
-        <v>0.7586993098929797</v>
+        <v>0.7136031350411498</v>
       </c>
       <c r="D78">
-        <v>2.87149930989298</v>
+        <v>2.85420313504115</v>
       </c>
       <c r="E78">
-        <v>1.7528</v>
+        <v>1.7806</v>
       </c>
       <c r="F78">
-        <v>2.1128</v>
+        <v>2.1406</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7671,45 +7671,45 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M78">
-        <v>0.11683784</v>
+        <v>0.12372668</v>
       </c>
       <c r="N78">
-        <v>0.4121621599999999</v>
+        <v>0.4052733199999999</v>
       </c>
       <c r="O78">
-        <v>0.06594594559999999</v>
+        <v>0.06484373119999999</v>
       </c>
       <c r="P78">
-        <v>0.3462162143999999</v>
+        <v>0.3404295888</v>
       </c>
       <c r="Q78">
-        <v>0.7562162144</v>
+        <v>0.7504295887999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2659008731355729</v>
+        <v>0.2750521330069735</v>
       </c>
       <c r="T78">
-        <v>3.029771365776529</v>
+        <v>3.155741902486173</v>
       </c>
       <c r="U78">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V78">
         <v>0.16</v>
       </c>
       <c r="W78">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>4.527642756832888</v>
+        <v>4.275553178990982</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1006470305916039</v>
+        <v>0.1005783316306703</v>
       </c>
       <c r="C79">
-        <v>0.7136031350411498</v>
+        <v>0.686576651275232</v>
       </c>
       <c r="D79">
-        <v>2.85420313504115</v>
+        <v>2.854976651275232</v>
       </c>
       <c r="E79">
-        <v>1.7806</v>
+        <v>1.8084</v>
       </c>
       <c r="F79">
-        <v>2.1406</v>
+        <v>2.1684</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7753,28 +7753,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M79">
-        <v>0.12372668</v>
+        <v>0.12533352</v>
       </c>
       <c r="N79">
-        <v>0.4052733199999999</v>
+        <v>0.4036664799999999</v>
       </c>
       <c r="O79">
-        <v>0.06484373119999999</v>
+        <v>0.06458663679999999</v>
       </c>
       <c r="P79">
-        <v>0.3404295888</v>
+        <v>0.3390798432</v>
       </c>
       <c r="Q79">
-        <v>0.7504295887999999</v>
+        <v>0.7490798431999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2750521330069735</v>
+        <v>0.285035325593956</v>
       </c>
       <c r="T79">
-        <v>3.155741902486173</v>
+        <v>3.293164306169421</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.275553178990982</v>
+        <v>4.220738394644943</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1005783316306703</v>
+        <v>0.1005096326697367</v>
       </c>
       <c r="C80">
-        <v>0.686576651275232</v>
+        <v>0.659550586883503</v>
       </c>
       <c r="D80">
-        <v>2.854976651275232</v>
+        <v>2.855750586883503</v>
       </c>
       <c r="E80">
-        <v>1.8084</v>
+        <v>1.8362</v>
       </c>
       <c r="F80">
-        <v>2.1684</v>
+        <v>2.1962</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7835,28 +7835,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M80">
-        <v>0.12533352</v>
+        <v>0.12694036</v>
       </c>
       <c r="N80">
-        <v>0.4036664799999999</v>
+        <v>0.4020596399999999</v>
       </c>
       <c r="O80">
-        <v>0.06458663679999999</v>
+        <v>0.06432954239999998</v>
       </c>
       <c r="P80">
-        <v>0.3390798432</v>
+        <v>0.3377300975999999</v>
       </c>
       <c r="Q80">
-        <v>0.7490798431999999</v>
+        <v>0.7477300975999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.285035325593956</v>
+        <v>0.2959692984273178</v>
       </c>
       <c r="T80">
-        <v>3.293164306169421</v>
+        <v>3.443674557822503</v>
       </c>
       <c r="U80">
         <v>0.0578</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.220738394644943</v>
+        <v>4.167311326358297</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1005096326697367</v>
+        <v>0.1004409337088032</v>
       </c>
       <c r="C81">
-        <v>0.659550586883503</v>
+        <v>0.6325249422071098</v>
       </c>
       <c r="D81">
-        <v>2.855750586883503</v>
+        <v>2.85652494220711</v>
       </c>
       <c r="E81">
-        <v>1.8362</v>
+        <v>1.864</v>
       </c>
       <c r="F81">
-        <v>2.1962</v>
+        <v>2.224</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7917,28 +7917,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M81">
-        <v>0.12694036</v>
+        <v>0.1285472</v>
       </c>
       <c r="N81">
-        <v>0.4020596399999999</v>
+        <v>0.4004527999999999</v>
       </c>
       <c r="O81">
-        <v>0.06432954239999998</v>
+        <v>0.06407244799999999</v>
       </c>
       <c r="P81">
-        <v>0.3377300975999999</v>
+        <v>0.3363803519999999</v>
       </c>
       <c r="Q81">
-        <v>0.7477300975999999</v>
+        <v>0.7463803519999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2959692984273178</v>
+        <v>0.3079966685440159</v>
       </c>
       <c r="T81">
-        <v>3.443674557822503</v>
+        <v>3.609235834640893</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.167311326358297</v>
+        <v>4.115219934778819</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1004409337088032</v>
+        <v>0.1003722347478696</v>
       </c>
       <c r="C82">
-        <v>0.6325249422071098</v>
+        <v>0.6054997175875698</v>
       </c>
       <c r="D82">
-        <v>2.85652494220711</v>
+        <v>2.85729971758757</v>
       </c>
       <c r="E82">
-        <v>1.864</v>
+        <v>1.8918</v>
       </c>
       <c r="F82">
-        <v>2.224</v>
+        <v>2.2518</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7999,28 +7999,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M82">
-        <v>0.1285472</v>
+        <v>0.13015404</v>
       </c>
       <c r="N82">
-        <v>0.4004527999999999</v>
+        <v>0.3988459599999999</v>
       </c>
       <c r="O82">
-        <v>0.06407244799999999</v>
+        <v>0.06381535359999999</v>
       </c>
       <c r="P82">
-        <v>0.3363803519999999</v>
+        <v>0.3350306063999999</v>
       </c>
       <c r="Q82">
-        <v>0.7463803519999999</v>
+        <v>0.7450306063999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3079966685440159</v>
+        <v>0.3212900776203663</v>
       </c>
       <c r="T82">
-        <v>3.609235834640893</v>
+        <v>3.792224614282271</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.115219934778819</v>
+        <v>4.064414750398835</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1003722347478696</v>
+        <v>0.100303535786936</v>
       </c>
       <c r="C83">
-        <v>0.6054997175875698</v>
+        <v>0.5784749133667733</v>
       </c>
       <c r="D83">
-        <v>2.85729971758757</v>
+        <v>2.858074913366773</v>
       </c>
       <c r="E83">
-        <v>1.8918</v>
+        <v>1.9196</v>
       </c>
       <c r="F83">
-        <v>2.2518</v>
+        <v>2.2796</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8081,28 +8081,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M83">
-        <v>0.13015404</v>
+        <v>0.13176088</v>
       </c>
       <c r="N83">
-        <v>0.3988459599999999</v>
+        <v>0.3972391199999999</v>
       </c>
       <c r="O83">
-        <v>0.06381535359999999</v>
+        <v>0.06355825919999999</v>
       </c>
       <c r="P83">
-        <v>0.3350306063999999</v>
+        <v>0.3336808607999999</v>
       </c>
       <c r="Q83">
-        <v>0.7450306063999999</v>
+        <v>0.7436808607999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3212900776203663</v>
+        <v>0.3360605321496444</v>
       </c>
       <c r="T83">
-        <v>3.792224614282271</v>
+        <v>3.995545480550469</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.064414750398835</v>
+        <v>4.014848716857386</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.100303535786936</v>
+        <v>0.1026750368260024</v>
       </c>
       <c r="C84">
-        <v>0.5784749133667733</v>
+        <v>0.5241561099464964</v>
       </c>
       <c r="D84">
-        <v>2.858074913366773</v>
+        <v>2.831556109946496</v>
       </c>
       <c r="E84">
-        <v>1.9196</v>
+        <v>1.9474</v>
       </c>
       <c r="F84">
-        <v>2.2796</v>
+        <v>2.3074</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8163,45 +8163,45 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M84">
-        <v>0.13176088</v>
+        <v>0.14144362</v>
       </c>
       <c r="N84">
-        <v>0.3972391199999999</v>
+        <v>0.3875563799999999</v>
       </c>
       <c r="O84">
-        <v>0.06355825919999999</v>
+        <v>0.06200902079999999</v>
       </c>
       <c r="P84">
-        <v>0.3336808607999999</v>
+        <v>0.3255473591999999</v>
       </c>
       <c r="Q84">
-        <v>0.7436808607999998</v>
+        <v>0.7355473591999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3360605321496444</v>
+        <v>0.352568687211779</v>
       </c>
       <c r="T84">
-        <v>3.995545480550469</v>
+        <v>4.222786448732573</v>
       </c>
       <c r="U84">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V84">
         <v>0.16</v>
       </c>
       <c r="W84">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y84">
-        <v>4.014848716857386</v>
+        <v>3.740006088645072</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1026750368260024</v>
+        <v>0.1026357378650688</v>
       </c>
       <c r="C85">
-        <v>0.5241561099464964</v>
+        <v>0.496791551647608</v>
       </c>
       <c r="D85">
-        <v>2.831556109946496</v>
+        <v>2.831991551647608</v>
       </c>
       <c r="E85">
-        <v>1.9474</v>
+        <v>1.9752</v>
       </c>
       <c r="F85">
-        <v>2.3074</v>
+        <v>2.3352</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8245,28 +8245,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M85">
-        <v>0.14144362</v>
+        <v>0.14314776</v>
       </c>
       <c r="N85">
-        <v>0.3875563799999999</v>
+        <v>0.38585224</v>
       </c>
       <c r="O85">
-        <v>0.06200902079999999</v>
+        <v>0.0617363584</v>
       </c>
       <c r="P85">
-        <v>0.3255473591999999</v>
+        <v>0.3241158815999999</v>
       </c>
       <c r="Q85">
-        <v>0.7355473591999999</v>
+        <v>0.7341158816</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.352568687211779</v>
+        <v>0.3711403616566802</v>
       </c>
       <c r="T85">
-        <v>4.222786448732573</v>
+        <v>4.478432537937439</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.740006088645072</v>
+        <v>3.695482206637394</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1026357378650688</v>
+        <v>0.1025964389041352</v>
       </c>
       <c r="C86">
-        <v>0.496791551647608</v>
+        <v>0.4694271272953054</v>
       </c>
       <c r="D86">
-        <v>2.831991551647608</v>
+        <v>2.832427127295305</v>
       </c>
       <c r="E86">
-        <v>1.9752</v>
+        <v>2.003</v>
       </c>
       <c r="F86">
-        <v>2.3352</v>
+        <v>2.363</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8327,28 +8327,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M86">
-        <v>0.14314776</v>
+        <v>0.1448519</v>
       </c>
       <c r="N86">
-        <v>0.38585224</v>
+        <v>0.3841480999999999</v>
       </c>
       <c r="O86">
-        <v>0.0617363584</v>
+        <v>0.06146369599999998</v>
       </c>
       <c r="P86">
-        <v>0.3241158815999999</v>
+        <v>0.3226844039999999</v>
       </c>
       <c r="Q86">
-        <v>0.7341158816</v>
+        <v>0.7326844039999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3711403616566801</v>
+        <v>0.3921882593609015</v>
       </c>
       <c r="T86">
-        <v>4.478432537937437</v>
+        <v>4.768164772369618</v>
       </c>
       <c r="U86">
         <v>0.0613</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.695482206637394</v>
+        <v>3.652005945382835</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1025964389041352</v>
+        <v>0.1025571399432016</v>
       </c>
       <c r="C87">
-        <v>0.4694271272953054</v>
+        <v>0.4420628369514055</v>
       </c>
       <c r="D87">
-        <v>2.832427127295305</v>
+        <v>2.832862836951405</v>
       </c>
       <c r="E87">
-        <v>2.003</v>
+        <v>2.0308</v>
       </c>
       <c r="F87">
-        <v>2.363</v>
+        <v>2.3908</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8409,28 +8409,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M87">
-        <v>0.1448519</v>
+        <v>0.14655604</v>
       </c>
       <c r="N87">
-        <v>0.3841480999999999</v>
+        <v>0.3824439599999999</v>
       </c>
       <c r="O87">
-        <v>0.06146369599999998</v>
+        <v>0.06119103359999999</v>
       </c>
       <c r="P87">
-        <v>0.3226844039999999</v>
+        <v>0.3212529263999999</v>
       </c>
       <c r="Q87">
-        <v>0.7326844039999998</v>
+        <v>0.7312529263999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3921882593609015</v>
+        <v>0.4162429995942974</v>
       </c>
       <c r="T87">
-        <v>4.768164772369618</v>
+        <v>5.099287326006397</v>
       </c>
       <c r="U87">
         <v>0.0613</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.652005945382835</v>
+        <v>3.609540759971408</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1025571399432016</v>
+        <v>0.1025178409822681</v>
       </c>
       <c r="C88">
-        <v>0.4420628369514055</v>
+        <v>0.4146986806777586</v>
       </c>
       <c r="D88">
-        <v>2.832862836951405</v>
+        <v>2.833298680677758</v>
       </c>
       <c r="E88">
-        <v>2.0308</v>
+        <v>2.0586</v>
       </c>
       <c r="F88">
-        <v>2.3908</v>
+        <v>2.4186</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8491,28 +8491,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M88">
-        <v>0.14655604</v>
+        <v>0.14826018</v>
       </c>
       <c r="N88">
-        <v>0.3824439599999999</v>
+        <v>0.38073982</v>
       </c>
       <c r="O88">
-        <v>0.06119103359999999</v>
+        <v>0.06091837119999999</v>
       </c>
       <c r="P88">
-        <v>0.3212529263999999</v>
+        <v>0.3198214488</v>
       </c>
       <c r="Q88">
-        <v>0.7312529263999998</v>
+        <v>0.7298214487999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4162429995942974</v>
+        <v>0.4439984690943697</v>
       </c>
       <c r="T88">
-        <v>5.099287326006397</v>
+        <v>5.481351810971912</v>
       </c>
       <c r="U88">
         <v>0.0613</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.609540759971408</v>
+        <v>3.568051785718863</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1025178409822681</v>
+        <v>0.1024785420213345</v>
       </c>
       <c r="C89">
-        <v>0.4146986806777586</v>
+        <v>0.3873346585362567</v>
       </c>
       <c r="D89">
-        <v>2.833298680677758</v>
+        <v>2.833734658536256</v>
       </c>
       <c r="E89">
-        <v>2.0586</v>
+        <v>2.0864</v>
       </c>
       <c r="F89">
-        <v>2.4186</v>
+        <v>2.4464</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8573,28 +8573,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M89">
-        <v>0.14826018</v>
+        <v>0.14996432</v>
       </c>
       <c r="N89">
-        <v>0.38073982</v>
+        <v>0.3790356799999999</v>
       </c>
       <c r="O89">
-        <v>0.06091837119999999</v>
+        <v>0.06064570879999999</v>
       </c>
       <c r="P89">
-        <v>0.3198214488</v>
+        <v>0.3183899712</v>
       </c>
       <c r="Q89">
-        <v>0.7298214487999999</v>
+        <v>0.7283899711999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4439984690943697</v>
+        <v>0.4763798501777873</v>
       </c>
       <c r="T89">
-        <v>5.481351810971912</v>
+        <v>5.927093710098346</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.568051785718863</v>
+        <v>3.52750574269933</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1024785420213345</v>
+        <v>0.1045325230604009</v>
       </c>
       <c r="C90">
-        <v>0.3873346585362567</v>
+        <v>0.3369263638666538</v>
       </c>
       <c r="D90">
-        <v>2.833734658536256</v>
+        <v>2.811126363866653</v>
       </c>
       <c r="E90">
-        <v>2.0864</v>
+        <v>2.1142</v>
       </c>
       <c r="F90">
-        <v>2.4464</v>
+        <v>2.4742</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8655,45 +8655,45 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M90">
-        <v>0.14996432</v>
+        <v>0.15859622</v>
       </c>
       <c r="N90">
-        <v>0.3790356799999999</v>
+        <v>0.37040378</v>
       </c>
       <c r="O90">
-        <v>0.06064570879999999</v>
+        <v>0.0592646048</v>
       </c>
       <c r="P90">
-        <v>0.3183899712</v>
+        <v>0.3111391752</v>
       </c>
       <c r="Q90">
-        <v>0.7283899711999999</v>
+        <v>0.7211391751999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4763798501777873</v>
+        <v>0.5146487550945535</v>
       </c>
       <c r="T90">
-        <v>5.927093710098346</v>
+        <v>6.453879590884131</v>
       </c>
       <c r="U90">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V90">
         <v>0.16</v>
       </c>
       <c r="W90">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y90">
-        <v>3.52750574269933</v>
+        <v>3.335514553877766</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1045325230604009</v>
+        <v>0.1045167440994673</v>
       </c>
       <c r="C91">
-        <v>0.3369263638666538</v>
+        <v>0.3092986687478856</v>
       </c>
       <c r="D91">
-        <v>2.811126363866653</v>
+        <v>2.811298668747885</v>
       </c>
       <c r="E91">
-        <v>2.1142</v>
+        <v>2.142</v>
       </c>
       <c r="F91">
-        <v>2.4742</v>
+        <v>2.502</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8737,28 +8737,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M91">
-        <v>0.15859622</v>
+        <v>0.1603782</v>
       </c>
       <c r="N91">
-        <v>0.37040378</v>
+        <v>0.3686217999999999</v>
       </c>
       <c r="O91">
-        <v>0.0592646048</v>
+        <v>0.05897948799999998</v>
       </c>
       <c r="P91">
-        <v>0.3111391752</v>
+        <v>0.3096423119999999</v>
       </c>
       <c r="Q91">
-        <v>0.7211391751999999</v>
+        <v>0.719642312</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5146487550945535</v>
+        <v>0.5605714409946733</v>
       </c>
       <c r="T91">
-        <v>6.453879590884131</v>
+        <v>7.086022647827074</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.335514553877766</v>
+        <v>3.298453281056901</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1045167440994673</v>
+        <v>0.1045009651385337</v>
       </c>
       <c r="C92">
-        <v>0.3092986687478856</v>
+        <v>0.2816709947528864</v>
       </c>
       <c r="D92">
-        <v>2.811298668747885</v>
+        <v>2.811470994752886</v>
       </c>
       <c r="E92">
-        <v>2.142</v>
+        <v>2.1698</v>
       </c>
       <c r="F92">
-        <v>2.502</v>
+        <v>2.5298</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8819,28 +8819,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M92">
-        <v>0.1603782</v>
+        <v>0.16216018</v>
       </c>
       <c r="N92">
-        <v>0.3686217999999999</v>
+        <v>0.3668398199999999</v>
       </c>
       <c r="O92">
-        <v>0.05897948799999998</v>
+        <v>0.05869437119999999</v>
       </c>
       <c r="P92">
-        <v>0.3096423119999999</v>
+        <v>0.3081454487999999</v>
       </c>
       <c r="Q92">
-        <v>0.719642312</v>
+        <v>0.7181454487999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5605714409946733</v>
+        <v>0.6166991682059305</v>
       </c>
       <c r="T92">
-        <v>7.086022647827074</v>
+        <v>7.858641939646226</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.298453281056901</v>
+        <v>3.262206541704628</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1045009651385337</v>
+        <v>0.1044851861776002</v>
       </c>
       <c r="C93">
-        <v>0.2816709947528864</v>
+        <v>0.254043341885541</v>
       </c>
       <c r="D93">
-        <v>2.811470994752886</v>
+        <v>2.811643341885541</v>
       </c>
       <c r="E93">
-        <v>2.1698</v>
+        <v>2.1976</v>
       </c>
       <c r="F93">
-        <v>2.5298</v>
+        <v>2.5576</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8901,28 +8901,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M93">
-        <v>0.16216018</v>
+        <v>0.16394216</v>
       </c>
       <c r="N93">
-        <v>0.3668398199999999</v>
+        <v>0.3650578399999999</v>
       </c>
       <c r="O93">
-        <v>0.05869437119999999</v>
+        <v>0.05840925439999999</v>
       </c>
       <c r="P93">
-        <v>0.3081454487999999</v>
+        <v>0.3066485855999999</v>
       </c>
       <c r="Q93">
-        <v>0.7181454487999999</v>
+        <v>0.7166485855999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6166991682059305</v>
+        <v>0.6868588272200021</v>
       </c>
       <c r="T93">
-        <v>7.858641939646226</v>
+        <v>8.824416054420167</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.262206541704628</v>
+        <v>3.226747774946968</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1044851861776002</v>
+        <v>0.1044694072166666</v>
       </c>
       <c r="C94">
-        <v>0.254043341885541</v>
+        <v>0.2264157101497353</v>
       </c>
       <c r="D94">
-        <v>2.811643341885541</v>
+        <v>2.811815710149735</v>
       </c>
       <c r="E94">
-        <v>2.1976</v>
+        <v>2.2254</v>
       </c>
       <c r="F94">
-        <v>2.5576</v>
+        <v>2.5854</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8983,28 +8983,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M94">
-        <v>0.16394216</v>
+        <v>0.16572414</v>
       </c>
       <c r="N94">
-        <v>0.3650578399999999</v>
+        <v>0.3632758599999999</v>
       </c>
       <c r="O94">
-        <v>0.05840925439999999</v>
+        <v>0.05812413759999999</v>
       </c>
       <c r="P94">
-        <v>0.3066485855999999</v>
+        <v>0.3051517223999999</v>
       </c>
       <c r="Q94">
-        <v>0.7166485855999999</v>
+        <v>0.7151517223999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6868588272200021</v>
+        <v>0.777064103095237</v>
       </c>
       <c r="T94">
-        <v>8.824416054420167</v>
+        <v>10.06612563055809</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.226747774946968</v>
+        <v>3.19205156231313</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1044694072166666</v>
+        <v>0.104453628255733</v>
       </c>
       <c r="C95">
-        <v>0.2264157101497353</v>
+        <v>0.1987880995493554</v>
       </c>
       <c r="D95">
-        <v>2.811815710149735</v>
+        <v>2.811988099549355</v>
       </c>
       <c r="E95">
-        <v>2.2254</v>
+        <v>2.2532</v>
       </c>
       <c r="F95">
-        <v>2.5854</v>
+        <v>2.6132</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9065,28 +9065,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M95">
-        <v>0.16572414</v>
+        <v>0.16750612</v>
       </c>
       <c r="N95">
-        <v>0.3632758599999999</v>
+        <v>0.3614938799999999</v>
       </c>
       <c r="O95">
-        <v>0.05812413759999999</v>
+        <v>0.05783902079999999</v>
       </c>
       <c r="P95">
-        <v>0.3051517223999999</v>
+        <v>0.3036548592</v>
       </c>
       <c r="Q95">
-        <v>0.7151517223999999</v>
+        <v>0.7136548591999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.777064103095237</v>
+        <v>0.8973378042622171</v>
       </c>
       <c r="T95">
-        <v>10.06612563055809</v>
+        <v>11.72173839874199</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.19205156231313</v>
+        <v>3.158093566969374</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.104453628255733</v>
+        <v>0.1044378492947994</v>
       </c>
       <c r="C96">
-        <v>0.1987880995493554</v>
+        <v>0.1711605100882894</v>
       </c>
       <c r="D96">
-        <v>2.811988099549355</v>
+        <v>2.812160510088289</v>
       </c>
       <c r="E96">
-        <v>2.2532</v>
+        <v>2.281</v>
       </c>
       <c r="F96">
-        <v>2.6132</v>
+        <v>2.641</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9147,28 +9147,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M96">
-        <v>0.16750612</v>
+        <v>0.1692881</v>
       </c>
       <c r="N96">
-        <v>0.3614938799999999</v>
+        <v>0.3597118999999999</v>
       </c>
       <c r="O96">
-        <v>0.05783902079999999</v>
+        <v>0.05755390399999998</v>
       </c>
       <c r="P96">
-        <v>0.3036548592</v>
+        <v>0.3021579959999999</v>
       </c>
       <c r="Q96">
-        <v>0.7136548591999999</v>
+        <v>0.7121579959999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8973378042622171</v>
+        <v>1.065720985895989</v>
       </c>
       <c r="T96">
-        <v>11.72173839874199</v>
+        <v>14.03959627419945</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.158093566969374</v>
+        <v>3.124850476790748</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1044378492947994</v>
+        <v>0.1044220703338658</v>
       </c>
       <c r="C97">
-        <v>0.1711605100882894</v>
+        <v>0.1435329417704256</v>
       </c>
       <c r="D97">
-        <v>2.812160510088289</v>
+        <v>2.812332941770426</v>
       </c>
       <c r="E97">
-        <v>2.281</v>
+        <v>2.3088</v>
       </c>
       <c r="F97">
-        <v>2.641</v>
+        <v>2.6688</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9229,28 +9229,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M97">
-        <v>0.1692881</v>
+        <v>0.17107008</v>
       </c>
       <c r="N97">
-        <v>0.3597118999999999</v>
+        <v>0.3579299199999999</v>
       </c>
       <c r="O97">
-        <v>0.05755390399999998</v>
+        <v>0.05726878719999998</v>
       </c>
       <c r="P97">
-        <v>0.3021579959999999</v>
+        <v>0.3006611327999999</v>
       </c>
       <c r="Q97">
-        <v>0.7121579959999998</v>
+        <v>0.7106611327999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.065720985895989</v>
+        <v>1.318295758346648</v>
       </c>
       <c r="T97">
-        <v>14.03959627419945</v>
+        <v>17.51638308738564</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.124850476790748</v>
+        <v>3.092299950990845</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1044220703338658</v>
+        <v>0.1044062913729322</v>
       </c>
       <c r="C98">
-        <v>0.1435329417704261</v>
+        <v>0.115905394599654</v>
       </c>
       <c r="D98">
-        <v>2.812332941770426</v>
+        <v>2.812505394599654</v>
       </c>
       <c r="E98">
-        <v>2.3088</v>
+        <v>2.3366</v>
       </c>
       <c r="F98">
-        <v>2.6688</v>
+        <v>2.6966</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9311,28 +9311,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M98">
-        <v>0.17107008</v>
+        <v>0.17285206</v>
       </c>
       <c r="N98">
-        <v>0.3579299199999999</v>
+        <v>0.3561479399999999</v>
       </c>
       <c r="O98">
-        <v>0.05726878719999998</v>
+        <v>0.05698367039999999</v>
       </c>
       <c r="P98">
-        <v>0.3006611327999999</v>
+        <v>0.2991642696</v>
       </c>
       <c r="Q98">
-        <v>0.7106611327999999</v>
+        <v>0.7091642696</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.318295758346644</v>
+        <v>1.739253712431073</v>
       </c>
       <c r="T98">
-        <v>17.5163830873856</v>
+        <v>23.31102777602923</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.092299950990845</v>
+        <v>3.060420570052795</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1044062913729322</v>
+        <v>0.1043905124119986</v>
       </c>
       <c r="C99">
-        <v>0.115905394599654</v>
+        <v>0.08827786857986419</v>
       </c>
       <c r="D99">
-        <v>2.812505394599654</v>
+        <v>2.812677868579864</v>
       </c>
       <c r="E99">
-        <v>2.3366</v>
+        <v>2.3644</v>
       </c>
       <c r="F99">
-        <v>2.6966</v>
+        <v>2.7244</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9393,28 +9393,28 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M99">
-        <v>0.17285206</v>
+        <v>0.17463404</v>
       </c>
       <c r="N99">
-        <v>0.3561479399999999</v>
+        <v>0.3543659599999999</v>
       </c>
       <c r="O99">
-        <v>0.05698367039999999</v>
+        <v>0.05669855359999999</v>
       </c>
       <c r="P99">
-        <v>0.2991642696</v>
+        <v>0.2976674063999999</v>
       </c>
       <c r="Q99">
-        <v>0.7091642696</v>
+        <v>0.7076674063999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.739253712431073</v>
+        <v>2.58116962059993</v>
       </c>
       <c r="T99">
-        <v>23.31102777602923</v>
+        <v>34.90031715331649</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.060420570052795</v>
+        <v>3.029191788725726</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1043905124119986</v>
+        <v>0.1108612134510651</v>
       </c>
       <c r="C100">
-        <v>0.08827786857986419</v>
+        <v>-0.008520145368243526</v>
       </c>
       <c r="D100">
-        <v>2.812677868579864</v>
+        <v>2.743679854631756</v>
       </c>
       <c r="E100">
-        <v>2.3644</v>
+        <v>2.3922</v>
       </c>
       <c r="F100">
-        <v>2.7244</v>
+        <v>2.7522</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9475,129 +9475,47 @@
         <v>0.5289999999999999</v>
       </c>
       <c r="M100">
-        <v>0.17463404</v>
+        <v>0.19788318</v>
       </c>
       <c r="N100">
-        <v>0.3543659599999999</v>
+        <v>0.3311168199999999</v>
       </c>
       <c r="O100">
-        <v>0.05669855359999999</v>
+        <v>0.05297869119999999</v>
       </c>
       <c r="P100">
-        <v>0.2976674063999999</v>
+        <v>0.2781381287999999</v>
       </c>
       <c r="Q100">
-        <v>0.7076674063999999</v>
+        <v>0.6881381287999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.58116962059993</v>
+        <v>5.106917345106501</v>
       </c>
       <c r="T100">
-        <v>34.90031715331649</v>
+        <v>69.66818528517825</v>
       </c>
       <c r="U100">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V100">
         <v>0.16</v>
       </c>
       <c r="W100">
-        <v>0.053844</v>
+        <v>0.06039600000000001</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y100">
-        <v>3.029191788725726</v>
+        <v>2.673294415422271</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1108612134510651</v>
-      </c>
-      <c r="C101">
-        <v>-0.008520145368243526</v>
-      </c>
-      <c r="D101">
-        <v>2.743679854631756</v>
-      </c>
-      <c r="E101">
-        <v>2.3922</v>
-      </c>
-      <c r="F101">
-        <v>2.7522</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>2.42</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="K101">
-        <v>0.41</v>
-      </c>
-      <c r="L101">
-        <v>0.5289999999999999</v>
-      </c>
-      <c r="M101">
-        <v>0.19788318</v>
-      </c>
-      <c r="N101">
-        <v>0.3311168199999999</v>
-      </c>
-      <c r="O101">
-        <v>0.05297869119999999</v>
-      </c>
-      <c r="P101">
-        <v>0.2781381287999999</v>
-      </c>
-      <c r="Q101">
-        <v>0.6881381287999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.106917345106501</v>
-      </c>
-      <c r="T101">
-        <v>69.66818528517825</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.16</v>
-      </c>
-      <c r="W101">
-        <v>0.06039600000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.673294415422271</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
